--- a/inventoryexportv2_1_updated.xlsx
+++ b/inventoryexportv2_1_updated.xlsx
@@ -1457,7 +1457,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" s="1" t="n">
         <v>0</v>
       </c>
@@ -1520,7 +1519,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" s="1" t="n">
         <v>0</v>
       </c>
@@ -1636,7 +1634,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" s="1" t="n">
         <v>0</v>
       </c>
@@ -1683,7 +1680,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="2" t="n"/>
       <c r="J6" s="2" t="n"/>
@@ -1734,7 +1730,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="2" t="n"/>
       <c r="J7" s="2" t="n"/>
@@ -1790,7 +1785,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="2" t="n"/>
       <c r="J8" s="2" t="n"/>
@@ -1896,7 +1890,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" s="1" t="n">
         <v>0</v>
       </c>
@@ -1943,7 +1936,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -2054,7 +2046,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" s="1" t="n">
         <v>0</v>
       </c>
@@ -2165,7 +2156,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
@@ -2227,7 +2217,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
@@ -2287,7 +2276,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="2" t="n"/>
       <c r="J17" s="2" t="n"/>
@@ -2345,7 +2333,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
@@ -2405,7 +2392,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="2" t="n"/>
       <c r="J19" s="2" t="n"/>
@@ -2461,7 +2447,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" s="1" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
@@ -2576,9 +2561,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" s="1" t="inlineStr"/>
-      <c r="I22" s="2" t="n"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>847294010113</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
@@ -2632,7 +2620,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" s="1" t="n">
         <v>0</v>
       </c>
@@ -2690,7 +2677,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" s="1" t="n">
         <v>0</v>
       </c>
@@ -2920,7 +2906,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="2" t="n"/>
       <c r="J28" s="2" t="n"/>
@@ -2971,9 +2956,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" s="1" t="inlineStr"/>
-      <c r="I29" s="2" t="n"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>676821169730</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="n"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
@@ -3017,7 +3005,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" s="1" t="n">
         <v>0</v>
       </c>
@@ -3064,7 +3051,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr">
         <is>
@@ -3180,7 +3166,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr">
         <is>
@@ -3230,7 +3215,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
@@ -3285,7 +3269,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr">
         <is>
@@ -3335,9 +3318,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" s="1" t="inlineStr"/>
-      <c r="I36" s="2" t="n"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>8472940071201</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="n"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
@@ -3386,7 +3372,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="2" t="n"/>
       <c r="J37" s="2" t="n"/>
@@ -3432,7 +3417,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="2" t="n"/>
       <c r="J38" s="2" t="n"/>
@@ -3483,7 +3467,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="2" t="n"/>
       <c r="J39" s="2" t="n"/>
@@ -3534,9 +3517,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" s="1" t="inlineStr"/>
-      <c r="I40" s="2" t="n"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>847294073873</t>
+        </is>
+      </c>
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
@@ -3585,7 +3571,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="2" t="n"/>
       <c r="J41" s="2" t="n"/>
@@ -3641,7 +3626,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr">
         <is>
@@ -3751,7 +3735,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" s="1" t="n">
         <v>0</v>
       </c>
@@ -3812,7 +3795,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr">
         <is>
@@ -3874,7 +3856,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" s="1" t="n">
         <v>0</v>
       </c>
@@ -3930,7 +3911,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" s="1" t="n">
         <v>0</v>
       </c>
@@ -3982,7 +3962,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="2" t="n"/>
       <c r="J48" s="2" t="n"/>
@@ -4023,7 +4002,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr">
         <is>
@@ -4078,7 +4056,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="2" t="n"/>
       <c r="J50" s="2" t="n"/>
@@ -4241,7 +4218,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr">
         <is>
@@ -4296,7 +4272,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr">
         <is>
@@ -4351,7 +4326,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="2" t="n"/>
       <c r="J55" s="2" t="n"/>
@@ -4397,7 +4371,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr">
         <is>
@@ -4452,7 +4425,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" s="1" t="n">
         <v>0</v>
       </c>
@@ -4508,7 +4480,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" s="1" t="n">
         <v>0</v>
       </c>
@@ -4558,7 +4529,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" s="1" t="n">
         <v>0</v>
       </c>
@@ -4608,9 +4578,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" s="1" t="inlineStr"/>
-      <c r="I60" s="2" t="n"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>676821422958</t>
+        </is>
+      </c>
       <c r="J60" s="2" t="n"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
@@ -4659,9 +4632,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" s="1" t="inlineStr"/>
-      <c r="I61" s="2" t="n"/>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>847294014036</t>
+        </is>
+      </c>
       <c r="J61" s="2" t="n"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
@@ -4710,7 +4686,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="2" t="n"/>
       <c r="J62" s="2" t="n"/>
@@ -4761,7 +4736,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="2" t="n"/>
       <c r="J63" s="2" t="n"/>
@@ -4812,7 +4786,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="2" t="n"/>
       <c r="J64" s="2" t="n"/>
@@ -4863,7 +4836,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr">
         <is>
@@ -4923,7 +4895,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" s="1" t="n">
         <v>0</v>
       </c>
@@ -5026,7 +4997,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="2" t="n"/>
       <c r="J68" s="2" t="n"/>
@@ -5072,7 +5042,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="2" t="n"/>
       <c r="J69" s="2" t="n"/>
@@ -5178,7 +5147,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr">
         <is>
@@ -5238,9 +5206,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" s="1" t="inlineStr"/>
-      <c r="I72" s="2" t="n"/>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>847294010175</t>
+        </is>
+      </c>
       <c r="J72" s="2" t="n"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
@@ -5354,7 +5325,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
       <c r="H74" s="1" t="n">
         <v>0</v>
       </c>
@@ -5401,7 +5371,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
       <c r="H75" s="1" t="n">
         <v>0</v>
       </c>
@@ -5509,7 +5478,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="2" t="n"/>
       <c r="J77" s="2" t="n"/>
@@ -5555,7 +5523,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" s="1" t="inlineStr"/>
       <c r="I78" s="2" t="n"/>
       <c r="J78" s="2" t="n"/>
@@ -5661,7 +5628,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" s="1" t="inlineStr"/>
       <c r="I80" s="2" t="inlineStr">
         <is>
@@ -5772,7 +5738,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" s="1" t="inlineStr"/>
       <c r="I82" s="2" t="n"/>
       <c r="J82" s="2" t="n"/>
@@ -5828,7 +5793,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
       <c r="H83" s="1" t="n">
         <v>0</v>
       </c>
@@ -5875,7 +5839,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" s="1" t="inlineStr"/>
       <c r="I84" s="2" t="n"/>
       <c r="J84" s="2" t="n"/>
@@ -5926,7 +5889,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" s="1" t="inlineStr"/>
       <c r="I85" s="2" t="n"/>
       <c r="J85" s="2" t="n"/>
@@ -6042,7 +6004,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
       <c r="H87" s="1" t="n">
         <v>0</v>
       </c>
@@ -6094,7 +6055,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
       <c r="H88" s="1" t="n">
         <v>0</v>
       </c>
@@ -6141,9 +6101,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
       <c r="H89" s="1" t="inlineStr"/>
-      <c r="I89" s="2" t="n"/>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>847294042107</t>
+        </is>
+      </c>
       <c r="J89" s="2" t="n"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
@@ -6192,7 +6155,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
       <c r="H90" s="1" t="n">
         <v>0</v>
       </c>
@@ -6244,7 +6206,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" s="1" t="inlineStr"/>
       <c r="I91" s="2" t="inlineStr">
         <is>
@@ -6299,7 +6260,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" s="1" t="n">
         <v>0</v>
       </c>
@@ -6356,7 +6316,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
       <c r="H93" s="1" t="n">
         <v>0</v>
       </c>
@@ -6403,7 +6362,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" s="1" t="inlineStr"/>
       <c r="I94" s="2" t="n"/>
       <c r="J94" s="2" t="n"/>
@@ -6454,7 +6412,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
       <c r="H95" s="1" t="inlineStr"/>
       <c r="I95" s="2" t="n"/>
       <c r="J95" s="2" t="n"/>
@@ -6505,7 +6462,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
       <c r="H96" s="1" t="inlineStr"/>
       <c r="I96" s="2" t="n"/>
       <c r="J96" s="2" t="n"/>
@@ -6551,7 +6507,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
       <c r="H97" s="1" t="n">
         <v>0</v>
       </c>
@@ -6599,7 +6554,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" s="1" t="inlineStr"/>
       <c r="I98" s="2" t="inlineStr">
         <is>
@@ -6656,7 +6610,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" s="1" t="n">
         <v>0</v>
       </c>
@@ -6712,7 +6665,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
       <c r="H100" s="1" t="n">
         <v>149.99</v>
       </c>
@@ -6769,7 +6721,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
       <c r="H101" s="1" t="n">
         <v>0</v>
       </c>
@@ -6826,9 +6777,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" s="1" t="inlineStr"/>
-      <c r="I102" s="2" t="n"/>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>676821441768</t>
+        </is>
+      </c>
       <c r="J102" s="2" t="n"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
@@ -6877,7 +6831,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
       <c r="H103" s="1" t="inlineStr"/>
       <c r="I103" s="2" t="inlineStr">
         <is>
@@ -6932,7 +6885,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
       <c r="H104" s="1" t="n">
         <v>0</v>
       </c>
@@ -6988,7 +6940,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
       <c r="H105" s="1" t="inlineStr"/>
       <c r="I105" s="2" t="n"/>
       <c r="J105" s="2" t="n"/>
@@ -7034,7 +6985,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
       <c r="H106" s="1" t="n">
         <v>0</v>
       </c>
@@ -7081,9 +7031,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
       <c r="H107" s="1" t="inlineStr"/>
-      <c r="I107" s="2" t="n"/>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>847294013305</t>
+        </is>
+      </c>
       <c r="J107" s="2" t="n"/>
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
@@ -7132,7 +7085,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
       <c r="H108" s="1" t="n">
         <v>0</v>
       </c>
@@ -7188,7 +7140,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
       <c r="H109" s="1" t="inlineStr"/>
       <c r="I109" s="2" t="n"/>
       <c r="J109" s="2" t="n"/>
@@ -7239,6 +7190,11 @@
           <t>Fixed</t>
         </is>
       </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>601527829435</t>
+        </is>
+      </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -7284,7 +7240,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
       <c r="H111" s="1" t="inlineStr"/>
       <c r="I111" s="2" t="inlineStr">
         <is>
@@ -7486,7 +7441,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
       <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="2" t="inlineStr">
         <is>
@@ -7743,7 +7697,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
       <c r="H119" s="1" t="inlineStr"/>
       <c r="I119" s="2" t="inlineStr">
         <is>
@@ -7864,7 +7817,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
       <c r="H122" s="1" t="inlineStr"/>
       <c r="I122" s="2" t="n"/>
       <c r="J122" s="2" t="n"/>
@@ -7977,7 +7929,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
       <c r="H124" s="1" t="n">
         <v>0</v>
       </c>
@@ -8024,7 +7975,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
       <c r="H125" s="1" t="inlineStr"/>
       <c r="I125" s="2" t="n"/>
       <c r="J125" s="2" t="n"/>
@@ -8141,7 +8091,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
       <c r="H127" s="1" t="inlineStr"/>
       <c r="I127" s="2" t="n"/>
       <c r="J127" s="2" t="n"/>
@@ -8257,7 +8206,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
       <c r="H129" s="1" t="n">
         <v>0</v>
       </c>
@@ -8309,7 +8257,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
       <c r="H130" s="1" t="n">
         <v>0</v>
       </c>
@@ -8430,7 +8377,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
       <c r="H132" s="1" t="n">
         <v>0</v>
       </c>
@@ -8616,7 +8562,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
       <c r="H136" s="1" t="n">
         <v>0</v>
       </c>
@@ -8672,7 +8617,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
       <c r="H137" s="1" t="n">
         <v>0</v>
       </c>
@@ -8729,7 +8673,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
       <c r="H138" s="1" t="n">
         <v>0</v>
       </c>
@@ -8776,7 +8719,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
       <c r="H139" s="1" t="inlineStr"/>
       <c r="I139" s="2" t="inlineStr">
         <is>
@@ -8831,7 +8773,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
       <c r="H140" s="1" t="n">
         <v>0</v>
       </c>
@@ -8882,7 +8823,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
       <c r="H141" s="1" t="n">
         <v>0</v>
       </c>
@@ -8943,7 +8883,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
       <c r="H142" s="1" t="n">
         <v>0</v>
       </c>
@@ -9004,7 +8943,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
       <c r="H143" s="1" t="inlineStr"/>
       <c r="I143" s="2" t="n"/>
       <c r="J143" s="2" t="n"/>
@@ -9055,7 +8993,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
       <c r="H144" s="1" t="n">
         <v>0</v>
       </c>
@@ -9107,7 +9044,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
       <c r="H145" s="1" t="inlineStr"/>
       <c r="I145" s="2" t="inlineStr">
         <is>
@@ -9228,7 +9164,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
       <c r="H147" s="1" t="inlineStr"/>
       <c r="I147" s="2" t="inlineStr">
         <is>
@@ -9283,7 +9218,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
       <c r="H148" s="1" t="inlineStr"/>
       <c r="I148" s="2" t="inlineStr">
         <is>
@@ -9338,9 +9272,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
       <c r="H149" s="1" t="inlineStr"/>
-      <c r="I149" s="2" t="n"/>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>601527746879</t>
+        </is>
+      </c>
       <c r="J149" s="2" t="n"/>
       <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="2" t="inlineStr">
@@ -9389,7 +9326,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
       <c r="H150" s="1" t="inlineStr"/>
       <c r="I150" s="2" t="n"/>
       <c r="J150" s="2" t="n"/>
@@ -9440,7 +9376,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
       <c r="H151" s="1" t="inlineStr"/>
       <c r="I151" s="2" t="n"/>
       <c r="J151" s="2" t="n"/>
@@ -9491,7 +9426,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr"/>
       <c r="H152" s="1" t="n">
         <v>0</v>
       </c>
@@ -9543,7 +9477,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr"/>
       <c r="H153" s="1" t="inlineStr"/>
       <c r="I153" s="2" t="n"/>
       <c r="J153" s="2" t="n"/>
@@ -9594,7 +9527,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr"/>
       <c r="H154" s="1" t="n">
         <v>0</v>
       </c>
@@ -9651,7 +9583,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr"/>
       <c r="H155" s="1" t="n">
         <v>0</v>
       </c>
@@ -9705,7 +9636,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr"/>
       <c r="H156" s="1" t="inlineStr"/>
       <c r="I156" s="2" t="inlineStr">
         <is>
@@ -9820,7 +9750,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr"/>
       <c r="H158" s="1" t="inlineStr"/>
       <c r="I158" s="2" t="n"/>
       <c r="J158" s="2" t="n"/>
@@ -9871,7 +9800,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr"/>
       <c r="H159" s="1" t="n">
         <v>0</v>
       </c>
@@ -9923,7 +9851,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr"/>
       <c r="H160" s="1" t="inlineStr"/>
       <c r="I160" s="2" t="n"/>
       <c r="J160" s="2" t="n"/>
@@ -9974,7 +9901,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr"/>
       <c r="H161" s="1" t="n">
         <v>0</v>
       </c>
@@ -10096,7 +10022,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr"/>
       <c r="H163" s="1" t="n">
         <v>0</v>
       </c>
@@ -10153,7 +10078,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr"/>
       <c r="H164" s="1" t="n">
         <v>0</v>
       </c>
@@ -10205,7 +10129,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr"/>
       <c r="H165" s="1" t="inlineStr"/>
       <c r="I165" s="2" t="n"/>
       <c r="J165" s="2" t="n"/>
@@ -10256,7 +10179,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr"/>
       <c r="H166" s="1" t="inlineStr"/>
       <c r="I166" s="2" t="inlineStr">
         <is>
@@ -10318,7 +10240,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr"/>
       <c r="H167" s="1" t="n">
         <v>0</v>
       </c>
@@ -10365,7 +10286,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr"/>
       <c r="H168" s="1" t="n">
         <v>0</v>
       </c>
@@ -10482,7 +10402,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
       <c r="H170" s="1" t="n">
         <v>0</v>
       </c>
@@ -10543,7 +10462,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr"/>
       <c r="H171" s="1" t="inlineStr"/>
       <c r="I171" s="2" t="inlineStr">
         <is>
@@ -10603,7 +10521,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr"/>
       <c r="H172" s="1" t="inlineStr"/>
       <c r="I172" s="2" t="inlineStr">
         <is>
@@ -10658,7 +10575,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr"/>
       <c r="H173" s="1" t="n">
         <v>0</v>
       </c>
@@ -10725,7 +10641,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr"/>
       <c r="H175" s="1" t="n">
         <v>0</v>
       </c>
@@ -11193,7 +11108,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr"/>
       <c r="H182" s="1" t="n">
         <v>0</v>
       </c>
@@ -11240,9 +11154,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr"/>
       <c r="H183" s="1" t="inlineStr"/>
-      <c r="I183" s="2" t="n"/>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>676821140685</t>
+        </is>
+      </c>
       <c r="J183" s="2" t="n"/>
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr">
@@ -11458,7 +11375,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr"/>
       <c r="H187" s="1" t="n">
         <v>0</v>
       </c>
@@ -11515,7 +11431,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr"/>
       <c r="H188" s="1" t="inlineStr"/>
       <c r="I188" s="2" t="inlineStr">
         <is>
@@ -11637,7 +11552,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr"/>
       <c r="H190" s="1" t="inlineStr"/>
       <c r="I190" s="2" t="n"/>
       <c r="J190" s="2" t="n"/>
@@ -11693,7 +11607,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr"/>
       <c r="H191" s="1" t="n">
         <v>0</v>
       </c>
@@ -11749,7 +11662,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr"/>
       <c r="H192" s="1" t="n">
         <v>0</v>
       </c>
@@ -11805,7 +11717,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr"/>
       <c r="H193" s="1" t="inlineStr"/>
       <c r="I193" s="2" t="inlineStr">
         <is>
@@ -11865,7 +11776,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr"/>
       <c r="H194" s="1" t="n">
         <v>0</v>
       </c>
@@ -11912,7 +11822,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr"/>
       <c r="H195" s="1" t="inlineStr"/>
       <c r="I195" s="2" t="n"/>
       <c r="J195" s="2" t="n"/>
@@ -11963,7 +11872,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr"/>
       <c r="H196" s="1" t="inlineStr"/>
       <c r="I196" s="2" t="inlineStr">
         <is>
@@ -12023,7 +11931,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr"/>
       <c r="H197" s="1" t="inlineStr"/>
       <c r="I197" s="2" t="inlineStr">
         <is>
@@ -12078,7 +11985,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr"/>
       <c r="H198" s="1" t="n">
         <v>0</v>
       </c>
@@ -12194,7 +12100,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr"/>
       <c r="H200" s="1" t="inlineStr"/>
       <c r="I200" s="2" t="inlineStr">
         <is>
@@ -12249,7 +12154,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr"/>
       <c r="H201" s="1" t="n">
         <v>0</v>
       </c>
@@ -12305,7 +12209,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr"/>
       <c r="H202" s="1" t="n">
         <v>0</v>
       </c>
@@ -12361,7 +12264,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr"/>
       <c r="H203" s="1" t="n">
         <v>0</v>
       </c>
@@ -12413,7 +12315,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr"/>
       <c r="H204" s="1" t="n">
         <v>0</v>
       </c>
@@ -12474,7 +12375,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr"/>
       <c r="H205" s="1" t="inlineStr"/>
       <c r="I205" s="2" t="n"/>
       <c r="J205" s="2" t="n"/>
@@ -12520,7 +12420,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr"/>
       <c r="H206" s="1" t="n">
         <v>0</v>
       </c>
@@ -12748,7 +12647,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr"/>
       <c r="H210" s="1" t="inlineStr"/>
       <c r="I210" s="2" t="n"/>
       <c r="J210" s="2" t="n"/>
@@ -12855,7 +12753,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr"/>
       <c r="H212" s="1" t="inlineStr"/>
       <c r="I212" s="2" t="n"/>
       <c r="J212" s="2" t="n"/>
@@ -12911,7 +12808,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr"/>
       <c r="H213" s="1" t="inlineStr"/>
       <c r="I213" s="2" t="inlineStr">
         <is>
@@ -12971,7 +12867,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr"/>
       <c r="H214" s="1" t="inlineStr"/>
       <c r="I214" s="2" t="n"/>
       <c r="J214" s="2" t="n"/>
@@ -13022,7 +12917,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr"/>
       <c r="H215" s="1" t="n">
         <v>0</v>
       </c>
@@ -13074,7 +12968,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr"/>
       <c r="H216" s="1" t="n">
         <v>0</v>
       </c>
@@ -13246,7 +13139,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr"/>
       <c r="H219" s="1" t="n">
         <v>0</v>
       </c>
@@ -13302,7 +13194,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr"/>
       <c r="H220" s="1" t="n">
         <v>0</v>
       </c>
@@ -13358,7 +13249,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr"/>
       <c r="H221" s="1" t="inlineStr"/>
       <c r="I221" s="2" t="n"/>
       <c r="J221" s="2" t="n"/>
@@ -13524,7 +13414,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr"/>
       <c r="H224" s="1" t="n">
         <v>0</v>
       </c>
@@ -13636,7 +13525,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr"/>
       <c r="H226" s="1" t="inlineStr"/>
       <c r="I226" s="2" t="inlineStr">
         <is>
@@ -13691,7 +13579,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr"/>
       <c r="H227" s="1" t="inlineStr"/>
       <c r="I227" s="2" t="n"/>
       <c r="J227" s="2" t="n"/>
@@ -13742,7 +13629,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr"/>
       <c r="H228" s="1" t="inlineStr"/>
       <c r="I228" s="2" t="inlineStr">
         <is>
@@ -13792,7 +13678,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr"/>
       <c r="H229" s="1" t="inlineStr"/>
       <c r="I229" s="2" t="inlineStr">
         <is>
@@ -13852,7 +13737,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr"/>
       <c r="H230" s="1" t="n">
         <v>0</v>
       </c>
@@ -13908,7 +13792,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr"/>
       <c r="H231" s="1" t="n">
         <v>0</v>
       </c>
@@ -13966,7 +13849,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr"/>
       <c r="H232" s="1" t="inlineStr"/>
       <c r="I232" s="2" t="inlineStr">
         <is>
@@ -14021,7 +13903,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr"/>
       <c r="H233" s="1" t="inlineStr"/>
       <c r="I233" s="2" t="inlineStr">
         <is>
@@ -14081,7 +13962,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr"/>
       <c r="H234" s="1" t="n">
         <v>0</v>
       </c>
@@ -14137,7 +14017,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr"/>
       <c r="H235" s="1" t="n">
         <v>0</v>
       </c>
@@ -14201,7 +14080,11 @@
       <c r="H236" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I236" s="2" t="n"/>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>847294032580</t>
+        </is>
+      </c>
       <c r="J236" s="2" t="n"/>
       <c r="K236" s="2" t="inlineStr"/>
       <c r="L236" s="2" t="inlineStr">
@@ -14245,7 +14128,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr"/>
       <c r="H237" s="1" t="n">
         <v>0</v>
       </c>
@@ -14297,7 +14179,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr"/>
       <c r="H238" s="1" t="n">
         <v>0</v>
       </c>
@@ -14355,7 +14236,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr"/>
       <c r="H239" s="1" t="inlineStr"/>
       <c r="I239" s="2" t="n"/>
       <c r="J239" s="2" t="n"/>
@@ -14406,7 +14286,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr"/>
       <c r="H240" s="1" t="n">
         <v>0</v>
       </c>
@@ -14462,7 +14341,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr"/>
       <c r="H241" s="1" t="inlineStr"/>
       <c r="I241" s="2" t="inlineStr">
         <is>
@@ -14517,7 +14395,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr"/>
       <c r="H242" s="1" t="n">
         <v>0</v>
       </c>
@@ -14564,7 +14441,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr"/>
       <c r="H243" s="1" t="inlineStr"/>
       <c r="I243" s="2" t="inlineStr">
         <is>
@@ -14624,7 +14500,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr"/>
       <c r="H244" s="1" t="n">
         <v>0</v>
       </c>
@@ -14735,7 +14610,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr"/>
       <c r="H246" s="1" t="inlineStr"/>
       <c r="I246" s="2" t="inlineStr">
         <is>
@@ -14790,7 +14664,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr"/>
       <c r="H247" s="1" t="n">
         <v>0</v>
       </c>
@@ -14846,7 +14719,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr"/>
       <c r="H248" s="1" t="n">
         <v>0</v>
       </c>
@@ -14902,7 +14774,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr"/>
       <c r="H249" s="1" t="inlineStr"/>
       <c r="I249" s="2" t="n"/>
       <c r="J249" s="2" t="n"/>
@@ -14958,7 +14829,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr"/>
       <c r="H250" s="1" t="inlineStr"/>
       <c r="I250" s="2" t="n"/>
       <c r="J250" s="2" t="n"/>
@@ -15014,7 +14884,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr"/>
       <c r="H251" s="1" t="inlineStr"/>
       <c r="I251" s="2" t="inlineStr">
         <is>
@@ -15074,7 +14943,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G252" t="inlineStr"/>
       <c r="H252" s="1" t="inlineStr"/>
       <c r="I252" s="2" t="inlineStr">
         <is>
@@ -15134,7 +15002,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr"/>
       <c r="H253" s="1" t="inlineStr"/>
       <c r="I253" s="2" t="n"/>
       <c r="J253" s="2" t="n"/>
@@ -15185,7 +15052,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr"/>
       <c r="H254" s="1" t="n">
         <v>0</v>
       </c>
@@ -15246,7 +15112,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G255" t="inlineStr"/>
       <c r="H255" s="1" t="n">
         <v>0</v>
       </c>
@@ -15302,7 +15167,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G256" t="inlineStr"/>
       <c r="H256" s="1" t="n">
         <v>0</v>
       </c>
@@ -15593,7 +15457,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr"/>
       <c r="H261" s="1" t="n">
         <v>0</v>
       </c>
@@ -15650,7 +15513,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr"/>
       <c r="H262" s="1" t="inlineStr"/>
       <c r="I262" s="2" t="inlineStr">
         <is>
@@ -15710,7 +15572,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr"/>
       <c r="H263" s="1" t="inlineStr"/>
       <c r="I263" s="2" t="inlineStr">
         <is>
@@ -15760,7 +15621,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr"/>
       <c r="H264" s="1" t="n">
         <v>0</v>
       </c>
@@ -15812,7 +15672,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr"/>
       <c r="H265" s="1" t="n">
         <v>0</v>
       </c>
@@ -15864,7 +15723,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr"/>
       <c r="H266" s="1" t="inlineStr"/>
       <c r="I266" s="2" t="inlineStr">
         <is>
@@ -15919,7 +15777,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr"/>
       <c r="H267" s="1" t="inlineStr"/>
       <c r="I267" s="2" t="n"/>
       <c r="J267" s="2" t="n"/>
@@ -16041,7 +15898,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr"/>
       <c r="H271" s="1" t="inlineStr"/>
       <c r="I271" s="2" t="inlineStr">
         <is>
@@ -16101,7 +15957,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr"/>
       <c r="H272" s="1" t="n">
         <v>0</v>
       </c>
@@ -16157,7 +16012,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr"/>
       <c r="H273" s="1" t="n">
         <v>0</v>
       </c>
@@ -16214,7 +16068,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G274" t="inlineStr"/>
       <c r="H274" s="1" t="n">
         <v>0</v>
       </c>
@@ -16345,7 +16198,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G276" t="inlineStr"/>
       <c r="H276" s="1" t="n">
         <v>0</v>
       </c>
@@ -16402,7 +16254,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G277" t="inlineStr"/>
       <c r="H277" s="1" t="inlineStr"/>
       <c r="I277" s="2" t="n"/>
       <c r="J277" s="2" t="n"/>
@@ -16453,7 +16304,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G278" t="inlineStr"/>
       <c r="H278" s="1" t="n">
         <v>0</v>
       </c>
@@ -16509,7 +16359,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G279" t="inlineStr"/>
       <c r="H279" s="1" t="n">
         <v>0</v>
       </c>
@@ -16565,7 +16414,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G280" t="inlineStr"/>
       <c r="H280" s="1" t="n">
         <v>0</v>
       </c>
@@ -16686,7 +16534,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G282" t="inlineStr"/>
       <c r="H282" s="1" t="n">
         <v>0</v>
       </c>
@@ -16733,7 +16580,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G283" t="inlineStr"/>
       <c r="H283" s="1" t="inlineStr"/>
       <c r="I283" s="2" t="n"/>
       <c r="J283" s="2" t="n"/>
@@ -16844,7 +16690,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G285" t="inlineStr"/>
       <c r="H285" s="1" t="inlineStr"/>
       <c r="I285" s="2" t="n"/>
       <c r="J285" s="2" t="n"/>
@@ -16900,7 +16745,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G286" t="inlineStr"/>
       <c r="H286" s="1" t="inlineStr"/>
       <c r="I286" s="2" t="inlineStr">
         <is>
@@ -17011,7 +16855,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G288" t="inlineStr"/>
       <c r="H288" s="1" t="inlineStr"/>
       <c r="I288" s="2" t="inlineStr">
         <is>
@@ -17117,9 +16960,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G290" t="inlineStr"/>
       <c r="H290" s="1" t="inlineStr"/>
-      <c r="I290" s="2" t="n"/>
+      <c r="I290" s="2" t="inlineStr">
+        <is>
+          <t>847294002019</t>
+        </is>
+      </c>
       <c r="J290" s="2" t="n"/>
       <c r="K290" s="2" t="inlineStr"/>
       <c r="L290" s="2" t="inlineStr">
@@ -17173,7 +17019,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G291" t="inlineStr"/>
       <c r="H291" s="1" t="inlineStr"/>
       <c r="I291" s="2" t="n"/>
       <c r="J291" s="2" t="n"/>
@@ -17229,7 +17074,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G292" t="inlineStr"/>
       <c r="H292" s="1" t="inlineStr"/>
       <c r="I292" s="2" t="inlineStr">
         <is>
@@ -17339,7 +17183,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G294" t="inlineStr"/>
       <c r="H294" s="1" t="inlineStr"/>
       <c r="I294" s="2" t="n"/>
       <c r="J294" s="2" t="n"/>
@@ -17455,7 +17298,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G296" t="inlineStr"/>
       <c r="H296" s="1" t="n">
         <v>0</v>
       </c>
@@ -17502,7 +17344,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G297" t="inlineStr"/>
       <c r="H297" s="1" t="n">
         <v>0</v>
       </c>
@@ -17553,7 +17394,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G298" t="inlineStr"/>
       <c r="H298" s="1" t="n">
         <v>0</v>
       </c>
@@ -17604,7 +17444,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G299" t="inlineStr"/>
       <c r="H299" s="1" t="inlineStr"/>
       <c r="I299" s="2" t="inlineStr">
         <is>
@@ -17719,7 +17558,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G301" t="inlineStr"/>
       <c r="H301" s="1" t="inlineStr"/>
       <c r="I301" s="2" t="inlineStr">
         <is>
@@ -17774,7 +17612,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G302" t="inlineStr"/>
       <c r="H302" s="1" t="inlineStr"/>
       <c r="I302" s="2" t="inlineStr">
         <is>
@@ -17829,7 +17666,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G303" t="inlineStr"/>
       <c r="H303" s="1" t="inlineStr"/>
       <c r="I303" s="2" t="inlineStr">
         <is>
@@ -17949,7 +17785,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G305" t="inlineStr"/>
       <c r="H305" s="1" t="inlineStr"/>
       <c r="I305" s="2" t="inlineStr">
         <is>
@@ -18004,7 +17839,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G306" t="inlineStr"/>
       <c r="H306" s="1" t="n">
         <v>0</v>
       </c>
@@ -18056,7 +17890,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G307" t="inlineStr"/>
       <c r="H307" s="1" t="inlineStr"/>
       <c r="I307" s="2" t="n"/>
       <c r="J307" s="2" t="n"/>
@@ -18107,7 +17940,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G308" t="inlineStr"/>
       <c r="H308" s="1" t="n">
         <v>0</v>
       </c>
@@ -18168,7 +18000,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G309" t="inlineStr"/>
       <c r="H309" s="1" t="n">
         <v>0</v>
       </c>
@@ -18229,7 +18060,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G310" t="inlineStr"/>
       <c r="H310" s="1" t="n">
         <v>0</v>
       </c>
@@ -18285,7 +18115,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G311" t="inlineStr"/>
       <c r="H311" s="1" t="inlineStr"/>
       <c r="I311" s="2" t="n"/>
       <c r="J311" s="2" t="n"/>
@@ -18336,7 +18165,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G312" t="inlineStr"/>
       <c r="H312" s="1" t="n">
         <v>0</v>
       </c>
@@ -18394,7 +18222,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G313" t="inlineStr"/>
       <c r="H313" s="1" t="inlineStr"/>
       <c r="I313" s="2" t="n"/>
       <c r="J313" s="2" t="n"/>
@@ -18501,7 +18328,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G315" t="inlineStr"/>
       <c r="H315" s="1" t="inlineStr"/>
       <c r="I315" s="2" t="n"/>
       <c r="J315" s="2" t="n"/>
@@ -18557,7 +18383,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G316" t="inlineStr"/>
       <c r="H316" s="1" t="inlineStr"/>
       <c r="I316" s="2" t="inlineStr">
         <is>
@@ -18617,7 +18442,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G317" t="inlineStr"/>
       <c r="H317" s="1" t="n">
         <v>0</v>
       </c>
@@ -18743,7 +18567,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G320" t="inlineStr"/>
       <c r="H320" s="1" t="n">
         <v>0</v>
       </c>
@@ -18859,7 +18682,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G322" t="inlineStr"/>
       <c r="H322" s="1" t="inlineStr"/>
       <c r="I322" s="2" t="n"/>
       <c r="J322" s="2" t="n"/>
@@ -18925,7 +18747,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G324" t="inlineStr"/>
       <c r="H324" s="1" t="inlineStr"/>
       <c r="I324" s="2" t="inlineStr">
         <is>
@@ -18980,7 +18801,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G325" t="inlineStr"/>
       <c r="H325" s="1" t="n">
         <v>0</v>
       </c>
@@ -19098,7 +18918,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G327" t="inlineStr"/>
       <c r="H327" s="1" t="n">
         <v>0</v>
       </c>
@@ -19150,7 +18969,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G328" t="inlineStr"/>
       <c r="H328" s="1" t="inlineStr"/>
       <c r="I328" s="2" t="n"/>
       <c r="J328" s="2" t="n"/>
@@ -19261,7 +19079,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G330" t="inlineStr"/>
       <c r="H330" s="1" t="inlineStr"/>
       <c r="I330" s="2" t="inlineStr">
         <is>
@@ -19316,7 +19133,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G331" t="inlineStr"/>
       <c r="H331" s="1" t="n">
         <v>0</v>
       </c>
@@ -19364,7 +19180,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G332" t="inlineStr"/>
       <c r="H332" s="1" t="n">
         <v>0</v>
       </c>
@@ -19411,7 +19226,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G333" t="inlineStr"/>
       <c r="H333" s="1" t="inlineStr"/>
       <c r="I333" s="2" t="inlineStr">
         <is>
@@ -19466,7 +19280,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G334" t="inlineStr"/>
       <c r="H334" s="1" t="n">
         <v>0</v>
       </c>
@@ -19578,7 +19391,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G336" t="inlineStr"/>
       <c r="H336" s="1" t="inlineStr"/>
       <c r="I336" s="2" t="inlineStr">
         <is>
@@ -19708,7 +19520,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G339" t="inlineStr"/>
       <c r="H339" s="1" t="inlineStr"/>
       <c r="I339" s="2" t="n"/>
       <c r="J339" s="2" t="n"/>
@@ -19815,7 +19626,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G341" t="inlineStr"/>
       <c r="H341" s="1" t="inlineStr"/>
       <c r="I341" s="2" t="n"/>
       <c r="J341" s="2" t="n"/>
@@ -19871,7 +19681,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G342" t="inlineStr"/>
       <c r="H342" s="1" t="n">
         <v>0</v>
       </c>
@@ -19927,7 +19736,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G343" t="inlineStr"/>
       <c r="H343" s="1" t="n">
         <v>0</v>
       </c>
@@ -20053,7 +19861,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G345" t="inlineStr"/>
       <c r="H345" s="1" t="inlineStr"/>
       <c r="I345" s="2" t="n"/>
       <c r="J345" s="2" t="n"/>
@@ -20109,7 +19916,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G346" t="inlineStr"/>
       <c r="H346" s="1" t="inlineStr"/>
       <c r="I346" s="2" t="inlineStr">
         <is>
@@ -20225,7 +20031,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G348" t="inlineStr"/>
       <c r="H348" s="1" t="inlineStr"/>
       <c r="I348" s="2" t="inlineStr">
         <is>
@@ -20270,7 +20075,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G349" t="inlineStr"/>
       <c r="H349" s="1" t="inlineStr"/>
       <c r="I349" s="2" t="inlineStr">
         <is>
@@ -20330,7 +20134,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G350" t="inlineStr"/>
       <c r="H350" s="1" t="inlineStr"/>
       <c r="I350" s="2" t="inlineStr">
         <is>
@@ -20440,7 +20243,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G352" t="inlineStr"/>
       <c r="H352" s="1" t="inlineStr"/>
       <c r="I352" s="2" t="inlineStr">
         <is>
@@ -20551,7 +20353,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G354" t="inlineStr"/>
       <c r="H354" s="1" t="inlineStr"/>
       <c r="I354" s="2" t="inlineStr">
         <is>
@@ -20671,7 +20472,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G356" t="inlineStr"/>
       <c r="H356" s="1" t="inlineStr"/>
       <c r="I356" s="2" t="inlineStr">
         <is>
@@ -20791,7 +20591,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G358" t="inlineStr"/>
       <c r="H358" s="1" t="inlineStr"/>
       <c r="I358" s="2" t="inlineStr">
         <is>
@@ -20902,9 +20701,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G360" t="inlineStr"/>
       <c r="H360" s="1" t="inlineStr"/>
-      <c r="I360" s="2" t="n"/>
+      <c r="I360" s="2" t="inlineStr">
+        <is>
+          <t>847294085579</t>
+        </is>
+      </c>
       <c r="J360" s="2" t="n"/>
       <c r="K360" s="2" t="inlineStr"/>
       <c r="L360" s="2" t="inlineStr">
@@ -21018,9 +20820,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G362" t="inlineStr"/>
       <c r="H362" s="1" t="inlineStr"/>
-      <c r="I362" s="2" t="n"/>
+      <c r="I362" s="2" t="inlineStr">
+        <is>
+          <t>847294085623</t>
+        </is>
+      </c>
       <c r="J362" s="2" t="n"/>
       <c r="K362" s="2" t="inlineStr"/>
       <c r="L362" s="2" t="inlineStr">
@@ -21134,9 +20939,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G364" t="inlineStr"/>
       <c r="H364" s="1" t="inlineStr"/>
-      <c r="I364" s="2" t="n"/>
+      <c r="I364" s="2" t="inlineStr">
+        <is>
+          <t>847294085609</t>
+        </is>
+      </c>
       <c r="J364" s="2" t="n"/>
       <c r="K364" s="2" t="inlineStr"/>
       <c r="L364" s="2" t="inlineStr">
@@ -21250,9 +21058,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G366" t="inlineStr"/>
       <c r="H366" s="1" t="inlineStr"/>
-      <c r="I366" s="2" t="n"/>
+      <c r="I366" s="2" t="inlineStr">
+        <is>
+          <t>847294085616</t>
+        </is>
+      </c>
       <c r="J366" s="2" t="n"/>
       <c r="K366" s="2" t="inlineStr"/>
       <c r="L366" s="2" t="inlineStr">
@@ -21426,7 +21237,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G369" t="inlineStr"/>
       <c r="H369" s="1" t="n">
         <v>0</v>
       </c>
@@ -21533,7 +21343,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G371" t="inlineStr"/>
       <c r="H371" s="1" t="inlineStr"/>
       <c r="I371" s="2" t="inlineStr">
         <is>
@@ -21593,7 +21402,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G372" t="inlineStr"/>
       <c r="H372" s="1" t="inlineStr"/>
       <c r="I372" s="2" t="inlineStr">
         <is>
@@ -21638,7 +21446,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G373" t="inlineStr"/>
       <c r="H373" s="1" t="n">
         <v>0</v>
       </c>
@@ -21690,7 +21497,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G374" t="inlineStr"/>
       <c r="H374" s="1" t="n">
         <v>0</v>
       </c>
@@ -21797,7 +21603,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G376" t="inlineStr"/>
       <c r="H376" s="1" t="inlineStr"/>
       <c r="I376" s="2" t="inlineStr">
         <is>
@@ -21847,9 +21652,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G377" t="inlineStr"/>
       <c r="H377" s="1" t="inlineStr"/>
-      <c r="I377" s="2" t="n"/>
+      <c r="I377" s="2" t="inlineStr">
+        <is>
+          <t>847294041735</t>
+        </is>
+      </c>
       <c r="J377" s="2" t="n"/>
       <c r="K377" s="2" t="inlineStr"/>
       <c r="L377" s="2" t="inlineStr">
@@ -21898,9 +21706,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G378" t="inlineStr"/>
       <c r="H378" s="1" t="inlineStr"/>
-      <c r="I378" s="2" t="n"/>
+      <c r="I378" s="2" t="inlineStr">
+        <is>
+          <t>847294041742</t>
+        </is>
+      </c>
       <c r="J378" s="2" t="n"/>
       <c r="K378" s="2" t="inlineStr"/>
       <c r="L378" s="2" t="inlineStr">
@@ -22066,7 +21877,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G381" t="inlineStr"/>
       <c r="H381" s="1" t="n">
         <v>0</v>
       </c>
@@ -22133,7 +21943,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G383" t="inlineStr"/>
       <c r="H383" s="1" t="n">
         <v>0</v>
       </c>
@@ -22184,7 +21993,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G384" t="inlineStr"/>
       <c r="H384" s="1" t="n">
         <v>0</v>
       </c>
@@ -22240,9 +22048,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G385" t="inlineStr"/>
       <c r="H385" s="1" t="inlineStr"/>
-      <c r="I385" s="2" t="n"/>
+      <c r="I385" s="2" t="inlineStr">
+        <is>
+          <t>847294036106</t>
+        </is>
+      </c>
       <c r="J385" s="2" t="n"/>
       <c r="K385" s="2" t="inlineStr"/>
       <c r="L385" s="2" t="inlineStr">
@@ -22412,7 +22223,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G388" t="inlineStr"/>
       <c r="H388" s="1" t="n">
         <v>0</v>
       </c>
@@ -22600,7 +22410,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G391" t="inlineStr"/>
       <c r="H391" s="1" t="n">
         <v>0</v>
       </c>
@@ -22716,9 +22525,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G393" t="inlineStr"/>
       <c r="H393" s="1" t="inlineStr"/>
-      <c r="I393" s="2" t="n"/>
+      <c r="I393" s="2" t="inlineStr">
+        <is>
+          <t>847294003016</t>
+        </is>
+      </c>
       <c r="J393" s="2" t="n"/>
       <c r="K393" s="2" t="inlineStr"/>
       <c r="L393" s="2" t="inlineStr">
@@ -22832,7 +22644,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G395" t="inlineStr"/>
       <c r="H395" s="1" t="inlineStr"/>
       <c r="I395" s="2" t="inlineStr">
         <is>
@@ -22889,7 +22700,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G396" t="inlineStr"/>
       <c r="H396" s="1" t="inlineStr"/>
       <c r="I396" s="2" t="inlineStr">
         <is>
@@ -22944,7 +22754,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G397" t="inlineStr"/>
       <c r="H397" s="1" t="n">
         <v>0</v>
       </c>
@@ -23060,7 +22869,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G399" t="inlineStr"/>
       <c r="H399" s="1" t="inlineStr"/>
       <c r="I399" s="2" t="n"/>
       <c r="J399" s="2" t="n"/>
@@ -23116,7 +22924,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G400" t="inlineStr"/>
       <c r="H400" s="1" t="inlineStr"/>
       <c r="I400" s="2" t="inlineStr">
         <is>
@@ -23161,7 +22968,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G401" t="inlineStr"/>
       <c r="H401" s="1" t="inlineStr"/>
       <c r="I401" s="2" t="inlineStr">
         <is>
@@ -23211,7 +23017,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G402" t="inlineStr"/>
       <c r="H402" s="1" t="n">
         <v>0</v>
       </c>
@@ -23328,7 +23133,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G404" t="inlineStr"/>
       <c r="H404" s="1" t="n">
         <v>0</v>
       </c>
@@ -23375,7 +23179,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G405" t="inlineStr"/>
       <c r="H405" s="1" t="inlineStr"/>
       <c r="I405" s="2" t="n"/>
       <c r="J405" s="2" t="n"/>
@@ -23431,9 +23234,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G406" t="inlineStr"/>
       <c r="H406" s="1" t="inlineStr"/>
-      <c r="I406" s="2" t="n"/>
+      <c r="I406" s="2" t="inlineStr">
+        <is>
+          <t>847294098722</t>
+        </is>
+      </c>
       <c r="J406" s="2" t="n"/>
       <c r="K406" s="2" t="inlineStr"/>
       <c r="L406" s="2" t="inlineStr">
@@ -23533,7 +23339,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G408" t="inlineStr"/>
       <c r="H408" s="1" t="inlineStr"/>
       <c r="I408" s="2" t="inlineStr">
         <is>
@@ -23649,7 +23454,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G410" t="inlineStr"/>
       <c r="H410" s="1" t="inlineStr"/>
       <c r="I410" s="2" t="n"/>
       <c r="J410" s="2" t="n"/>
@@ -23705,7 +23509,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G411" t="inlineStr"/>
       <c r="H411" s="1" t="n">
         <v>0</v>
       </c>
@@ -23761,7 +23564,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G412" t="inlineStr"/>
       <c r="H412" s="1" t="inlineStr"/>
       <c r="I412" s="2" t="inlineStr">
         <is>
@@ -23816,7 +23618,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G413" t="inlineStr"/>
       <c r="H413" s="1" t="n">
         <v>0</v>
       </c>
@@ -23872,7 +23673,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G414" t="inlineStr"/>
       <c r="H414" s="1" t="n">
         <v>0</v>
       </c>
@@ -24050,7 +23850,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G417" t="inlineStr"/>
       <c r="H417" s="1" t="inlineStr"/>
       <c r="I417" s="2" t="inlineStr">
         <is>
@@ -24110,7 +23909,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G418" t="inlineStr"/>
       <c r="H418" s="1" t="n">
         <v>0</v>
       </c>
@@ -24162,7 +23960,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G419" t="inlineStr"/>
       <c r="H419" s="1" t="inlineStr"/>
       <c r="I419" s="2" t="inlineStr">
         <is>
@@ -24217,7 +24014,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G420" t="inlineStr"/>
       <c r="H420" s="1" t="n">
         <v>0</v>
       </c>
@@ -24278,9 +24074,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G421" t="inlineStr"/>
       <c r="H421" s="1" t="inlineStr"/>
-      <c r="I421" s="2" t="n"/>
+      <c r="I421" s="2" t="inlineStr">
+        <is>
+          <t>847294096100</t>
+        </is>
+      </c>
       <c r="J421" s="2" t="n"/>
       <c r="K421" s="2" t="inlineStr"/>
       <c r="L421" s="2" t="inlineStr">
@@ -24329,7 +24128,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G422" t="inlineStr"/>
       <c r="H422" s="1" t="n">
         <v>0</v>
       </c>
@@ -24376,7 +24174,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G423" t="inlineStr"/>
       <c r="H423" s="1" t="inlineStr"/>
       <c r="I423" s="2" t="n"/>
       <c r="J423" s="2" t="n"/>
@@ -24442,7 +24239,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G425" t="inlineStr"/>
       <c r="H425" s="1" t="inlineStr"/>
       <c r="I425" s="2" t="n"/>
       <c r="J425" s="2" t="n"/>
@@ -24498,7 +24294,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G426" t="inlineStr"/>
       <c r="H426" s="1" t="inlineStr"/>
       <c r="I426" s="2" t="inlineStr">
         <is>
@@ -24558,7 +24353,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G427" t="inlineStr"/>
       <c r="H427" s="1" t="n">
         <v>0</v>
       </c>
@@ -24615,7 +24409,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G428" t="inlineStr"/>
       <c r="H428" s="1" t="inlineStr"/>
       <c r="I428" s="2" t="inlineStr">
         <is>
@@ -24670,7 +24463,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G429" t="inlineStr"/>
       <c r="H429" s="1" t="inlineStr"/>
       <c r="I429" s="2" t="inlineStr">
         <is>
@@ -24730,7 +24522,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G430" t="inlineStr"/>
       <c r="H430" s="1" t="n">
         <v>0</v>
       </c>
@@ -24787,7 +24578,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G431" t="inlineStr"/>
       <c r="H431" s="1" t="inlineStr"/>
       <c r="I431" s="2" t="inlineStr">
         <is>
@@ -24859,7 +24649,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G433" t="inlineStr"/>
       <c r="H433" s="1" t="n">
         <v>0</v>
       </c>
@@ -24920,7 +24709,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G434" t="inlineStr"/>
       <c r="H434" s="1" t="n">
         <v>0</v>
       </c>
@@ -24977,7 +24765,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G435" t="inlineStr"/>
       <c r="H435" s="1" t="inlineStr"/>
       <c r="I435" s="2" t="inlineStr">
         <is>
@@ -25032,7 +24819,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G436" t="inlineStr"/>
       <c r="H436" s="1" t="inlineStr"/>
       <c r="I436" s="2" t="inlineStr">
         <is>
@@ -25092,7 +24878,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G437" t="inlineStr"/>
       <c r="H437" s="1" t="n">
         <v>0</v>
       </c>
@@ -25149,7 +24934,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G438" t="inlineStr"/>
       <c r="H438" s="1" t="inlineStr"/>
       <c r="I438" s="2" t="n"/>
       <c r="J438" s="2" t="n"/>
@@ -25200,7 +24984,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G439" t="inlineStr"/>
       <c r="H439" s="1" t="inlineStr"/>
       <c r="I439" s="2" t="inlineStr">
         <is>
@@ -25250,7 +25033,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G440" t="inlineStr"/>
       <c r="H440" s="1" t="n">
         <v>0</v>
       </c>
@@ -25307,7 +25089,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G441" t="inlineStr"/>
       <c r="H441" s="1" t="n">
         <v>0</v>
       </c>
@@ -25359,7 +25140,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G442" t="inlineStr"/>
       <c r="H442" s="1" t="inlineStr"/>
       <c r="I442" s="2" t="inlineStr">
         <is>
@@ -25404,7 +25184,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G443" t="inlineStr"/>
       <c r="H443" s="1" t="inlineStr"/>
       <c r="I443" s="2" t="inlineStr">
         <is>
@@ -25469,7 +25248,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G445" t="inlineStr"/>
       <c r="H445" s="1" t="n">
         <v>0</v>
       </c>
@@ -25639,7 +25417,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G448" t="inlineStr"/>
       <c r="H448" s="1" t="n">
         <v>0</v>
       </c>
@@ -25690,7 +25467,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G449" t="inlineStr"/>
       <c r="H449" s="1" t="n">
         <v>0</v>
       </c>
@@ -25866,7 +25642,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G452" t="inlineStr"/>
       <c r="H452" s="1" t="n">
         <v>0</v>
       </c>
@@ -25922,7 +25697,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G453" t="inlineStr"/>
       <c r="H453" s="1" t="n">
         <v>0</v>
       </c>
@@ -25983,7 +25757,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G454" t="inlineStr"/>
       <c r="H454" s="1" t="n">
         <v>0</v>
       </c>
@@ -26044,7 +25817,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G455" t="inlineStr"/>
       <c r="H455" s="1" t="n">
         <v>0</v>
       </c>
@@ -26217,7 +25989,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G458" t="inlineStr"/>
       <c r="H458" s="1" t="inlineStr"/>
       <c r="I458" s="2" t="inlineStr">
         <is>
@@ -26277,7 +26048,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G459" t="inlineStr"/>
       <c r="H459" s="1" t="inlineStr"/>
       <c r="I459" s="2" t="inlineStr">
         <is>
@@ -26332,7 +26102,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G460" t="inlineStr"/>
       <c r="H460" s="1" t="n">
         <v>0</v>
       </c>
@@ -26454,9 +26223,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G462" t="inlineStr"/>
       <c r="H462" s="1" t="inlineStr"/>
-      <c r="I462" s="2" t="n"/>
+      <c r="I462" s="2" t="inlineStr">
+        <is>
+          <t>847294016726</t>
+        </is>
+      </c>
       <c r="J462" s="2" t="n"/>
       <c r="K462" s="2" t="inlineStr"/>
       <c r="L462" s="2" t="inlineStr">
@@ -26510,7 +26282,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G463" t="inlineStr"/>
       <c r="H463" s="1" t="n">
         <v>0</v>
       </c>
@@ -26571,7 +26342,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G464" t="inlineStr"/>
       <c r="H464" s="1" t="n">
         <v>0</v>
       </c>
@@ -26623,7 +26393,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G465" t="inlineStr"/>
       <c r="H465" s="1" t="n">
         <v>0</v>
       </c>
@@ -26681,7 +26450,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G466" t="inlineStr"/>
       <c r="H466" s="1" t="inlineStr"/>
       <c r="I466" s="2" t="n"/>
       <c r="J466" s="2" t="n"/>
@@ -26734,7 +26502,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G467" t="inlineStr"/>
       <c r="H467" s="1" t="n">
         <v>0</v>
       </c>
@@ -26793,7 +26560,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G468" t="inlineStr"/>
       <c r="H468" s="1" t="inlineStr"/>
       <c r="I468" s="2" t="n"/>
       <c r="J468" s="2" t="n"/>
@@ -26846,7 +26612,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G469" t="inlineStr"/>
       <c r="H469" s="1" t="n">
         <v>0</v>
       </c>
@@ -26903,7 +26668,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G470" t="inlineStr"/>
       <c r="H470" s="1" t="n">
         <v>0</v>
       </c>
@@ -26959,7 +26723,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G471" t="inlineStr"/>
       <c r="H471" s="1" t="inlineStr"/>
       <c r="I471" s="2" t="n"/>
       <c r="J471" s="2" t="n"/>
@@ -27010,7 +26773,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G472" t="inlineStr"/>
       <c r="H472" s="1" t="n">
         <v>0</v>
       </c>
@@ -27121,7 +26883,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G474" t="inlineStr"/>
       <c r="H474" s="1" t="n">
         <v>0</v>
       </c>
@@ -27178,7 +26939,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G475" t="inlineStr"/>
       <c r="H475" s="1" t="n">
         <v>0</v>
       </c>
@@ -27230,9 +26990,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G476" t="inlineStr"/>
       <c r="H476" s="1" t="inlineStr"/>
-      <c r="I476" s="2" t="n"/>
+      <c r="I476" s="2" t="inlineStr">
+        <is>
+          <t>676821147899</t>
+        </is>
+      </c>
       <c r="J476" s="2" t="n"/>
       <c r="K476" s="2" t="inlineStr"/>
       <c r="L476" s="2" t="inlineStr">
@@ -27281,7 +27044,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G477" t="inlineStr"/>
       <c r="H477" s="1" t="inlineStr"/>
       <c r="I477" s="2" t="inlineStr">
         <is>
@@ -27340,9 +27102,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G478" t="inlineStr"/>
       <c r="H478" s="1" t="inlineStr"/>
-      <c r="I478" s="2" t="n"/>
+      <c r="I478" s="2" t="inlineStr">
+        <is>
+          <t>847294019239</t>
+        </is>
+      </c>
       <c r="J478" s="2" t="n"/>
       <c r="K478" s="2" t="inlineStr"/>
       <c r="L478" s="2" t="inlineStr">
@@ -27508,7 +27273,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G481" t="inlineStr"/>
       <c r="H481" s="1" t="n">
         <v>0</v>
       </c>
@@ -27560,7 +27324,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G482" t="inlineStr"/>
       <c r="H482" s="1" t="inlineStr"/>
       <c r="I482" s="2" t="n"/>
       <c r="J482" s="2" t="n"/>
@@ -27611,11 +27374,14 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G483" t="inlineStr"/>
       <c r="H483" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I483" s="2" t="n"/>
+      <c r="I483" s="2" t="inlineStr">
+        <is>
+          <t>676821181657</t>
+        </is>
+      </c>
       <c r="J483" s="2" t="n"/>
       <c r="K483" s="2" t="inlineStr"/>
       <c r="L483" s="2" t="inlineStr">
@@ -27664,7 +27430,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G484" t="inlineStr"/>
       <c r="H484" s="1" t="n">
         <v>0</v>
       </c>
@@ -27721,9 +27486,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G485" t="inlineStr"/>
       <c r="H485" s="1" t="inlineStr"/>
-      <c r="I485" s="2" t="n"/>
+      <c r="I485" s="2" t="inlineStr">
+        <is>
+          <t>676821181657</t>
+        </is>
+      </c>
       <c r="J485" s="2" t="n"/>
       <c r="K485" s="2" t="inlineStr"/>
       <c r="L485" s="2" t="inlineStr">
@@ -27772,7 +27540,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G486" t="inlineStr"/>
       <c r="H486" s="1" t="n">
         <v>0</v>
       </c>
@@ -27824,7 +27591,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G487" t="inlineStr"/>
       <c r="H487" s="1" t="inlineStr"/>
       <c r="I487" s="2" t="n"/>
       <c r="J487" s="2" t="n"/>
@@ -27875,7 +27641,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G488" t="inlineStr"/>
       <c r="H488" s="1" t="inlineStr"/>
       <c r="I488" s="2" t="inlineStr">
         <is>
@@ -27995,7 +27760,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G490" t="inlineStr"/>
       <c r="H490" s="1" t="n">
         <v>0</v>
       </c>
@@ -28052,7 +27816,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G491" t="inlineStr"/>
       <c r="H491" s="1" t="inlineStr"/>
       <c r="I491" s="2" t="inlineStr">
         <is>
@@ -28158,7 +27921,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G493" t="inlineStr"/>
       <c r="H493" s="1" t="n">
         <v>0</v>
       </c>
@@ -28210,7 +27972,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G494" t="inlineStr"/>
       <c r="H494" s="1" t="inlineStr"/>
       <c r="I494" s="2" t="inlineStr">
         <is>
@@ -28265,7 +28026,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G495" t="inlineStr"/>
       <c r="H495" s="1" t="n">
         <v>0</v>
       </c>
@@ -28321,7 +28081,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G496" t="inlineStr"/>
       <c r="H496" s="1" t="inlineStr"/>
       <c r="I496" s="2" t="inlineStr">
         <is>
@@ -28371,7 +28130,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G497" t="inlineStr"/>
       <c r="H497" s="1" t="inlineStr"/>
       <c r="I497" s="2" t="inlineStr">
         <is>
@@ -28486,7 +28244,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G499" t="inlineStr"/>
       <c r="H499" s="1" t="n">
         <v>0</v>
       </c>
@@ -28543,7 +28300,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G500" t="inlineStr"/>
       <c r="H500" s="1" t="n">
         <v>0</v>
       </c>
@@ -28600,7 +28356,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G501" t="inlineStr"/>
       <c r="H501" s="1" t="n">
         <v>0</v>
       </c>
@@ -28656,7 +28411,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G502" t="inlineStr"/>
       <c r="H502" s="1" t="inlineStr"/>
       <c r="I502" s="2" t="n"/>
       <c r="J502" s="2" t="n"/>
@@ -28842,7 +28596,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G505" t="inlineStr"/>
       <c r="H505" s="1" t="inlineStr"/>
       <c r="I505" s="2" t="n"/>
       <c r="J505" s="2" t="n"/>
@@ -28898,7 +28651,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G506" t="inlineStr"/>
       <c r="H506" s="1" t="inlineStr"/>
       <c r="I506" s="2" t="inlineStr">
         <is>
@@ -28953,7 +28705,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G507" t="inlineStr"/>
       <c r="H507" s="1" t="inlineStr"/>
       <c r="I507" s="2" t="inlineStr">
         <is>
@@ -29013,7 +28764,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G508" t="inlineStr"/>
       <c r="H508" s="1" t="n">
         <v>0</v>
       </c>
@@ -29070,7 +28820,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G509" t="inlineStr"/>
       <c r="H509" s="1" t="n">
         <v>0</v>
       </c>
@@ -29122,7 +28871,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G510" t="inlineStr"/>
       <c r="H510" s="1" t="n">
         <v>0</v>
       </c>
@@ -29249,7 +28997,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G512" t="inlineStr"/>
       <c r="H512" s="1" t="n">
         <v>0</v>
       </c>
@@ -29296,7 +29043,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G513" t="inlineStr"/>
       <c r="H513" s="1" t="n">
         <v>0</v>
       </c>
@@ -29352,9 +29098,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G514" t="inlineStr"/>
       <c r="H514" s="1" t="inlineStr"/>
-      <c r="I514" s="2" t="n"/>
+      <c r="I514" s="2" t="inlineStr">
+        <is>
+          <t>847294017013</t>
+        </is>
+      </c>
       <c r="J514" s="2" t="n"/>
       <c r="K514" s="2" t="inlineStr"/>
       <c r="L514" s="2" t="inlineStr">
@@ -29408,7 +29157,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G515" t="inlineStr"/>
       <c r="H515" s="1" t="n">
         <v>0</v>
       </c>
@@ -29455,7 +29203,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G516" t="inlineStr"/>
       <c r="H516" s="1" t="inlineStr"/>
       <c r="I516" s="2" t="n"/>
       <c r="J516" s="2" t="n"/>
@@ -29506,7 +29253,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G517" t="inlineStr"/>
       <c r="H517" s="1" t="inlineStr"/>
       <c r="I517" s="45" t="n">
         <v>690220330508</v>
@@ -29569,7 +29315,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G519" t="inlineStr"/>
       <c r="H519" s="1" t="n">
         <v>0</v>
       </c>
@@ -29616,7 +29361,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G520" t="inlineStr"/>
       <c r="H520" s="1" t="n">
         <v>0</v>
       </c>
@@ -29672,7 +29416,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G521" t="inlineStr"/>
       <c r="H521" s="1" t="n">
         <v>0</v>
       </c>
@@ -29733,7 +29476,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G522" t="inlineStr"/>
       <c r="H522" s="1" t="n">
         <v>0</v>
       </c>
@@ -29789,7 +29531,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G523" t="inlineStr"/>
       <c r="H523" s="1" t="n">
         <v>0</v>
       </c>
@@ -29896,7 +29637,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G525" t="inlineStr"/>
       <c r="H525" s="1" t="inlineStr"/>
       <c r="I525" s="2" t="n"/>
       <c r="J525" s="2" t="n"/>
@@ -29952,7 +29692,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G526" t="inlineStr"/>
       <c r="H526" s="1" t="inlineStr"/>
       <c r="I526" s="2" t="inlineStr">
         <is>
@@ -30010,7 +29749,6 @@
           <t>Variable</t>
         </is>
       </c>
-      <c r="G527" t="inlineStr"/>
       <c r="H527" s="1" t="n">
         <v>0</v>
       </c>
@@ -30057,7 +29795,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G528" t="inlineStr"/>
       <c r="H528" s="1" t="n">
         <v>0</v>
       </c>
@@ -30109,7 +29846,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G529" t="inlineStr"/>
       <c r="H529" s="1" t="inlineStr"/>
       <c r="I529" s="2" t="inlineStr">
         <is>
@@ -30159,7 +29895,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G530" t="inlineStr"/>
       <c r="H530" s="1" t="inlineStr"/>
       <c r="I530" s="2" t="inlineStr">
         <is>
@@ -30219,7 +29954,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G531" t="inlineStr"/>
       <c r="H531" s="1" t="inlineStr"/>
       <c r="I531" s="2" t="inlineStr">
         <is>
@@ -30279,7 +30013,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G532" t="inlineStr"/>
       <c r="H532" s="1" t="inlineStr"/>
       <c r="I532" s="2" t="n"/>
       <c r="J532" s="2" t="n"/>
@@ -30335,7 +30068,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G533" t="inlineStr"/>
       <c r="H533" s="1" t="n">
         <v>0</v>
       </c>
@@ -30396,7 +30128,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G534" t="inlineStr"/>
       <c r="H534" s="1" t="inlineStr"/>
       <c r="I534" s="2" t="n"/>
       <c r="J534" s="2" t="n"/>
@@ -30447,7 +30178,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G535" t="inlineStr"/>
       <c r="H535" s="1" t="n">
         <v>0</v>
       </c>
@@ -30503,7 +30233,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G536" t="inlineStr"/>
       <c r="H536" s="1" t="inlineStr"/>
       <c r="I536" s="2" t="n"/>
       <c r="J536" s="2" t="n"/>
@@ -30554,7 +30283,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G537" t="inlineStr"/>
       <c r="H537" s="1" t="n">
         <v>0</v>
       </c>
@@ -30670,7 +30398,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G539" t="inlineStr"/>
       <c r="H539" s="1" t="n">
         <v>0</v>
       </c>
@@ -30722,7 +30449,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G540" t="inlineStr"/>
       <c r="H540" s="1" t="n">
         <v>0</v>
       </c>
@@ -30769,7 +30495,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G541" t="inlineStr"/>
       <c r="H541" s="1" t="n">
         <v>0</v>
       </c>
@@ -30826,7 +30551,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G542" t="inlineStr"/>
       <c r="H542" s="1" t="inlineStr"/>
       <c r="I542" s="2" t="n"/>
       <c r="J542" s="2" t="n"/>
@@ -30877,7 +30601,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G543" t="inlineStr"/>
       <c r="H543" s="1" t="n">
         <v>0</v>
       </c>
@@ -30933,7 +30656,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G544" t="inlineStr"/>
       <c r="H544" s="1" t="inlineStr"/>
       <c r="I544" s="2" t="inlineStr">
         <is>
@@ -30988,7 +30710,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G545" t="inlineStr"/>
       <c r="H545" s="1" t="inlineStr"/>
       <c r="I545" s="2" t="n"/>
       <c r="J545" s="2" t="n"/>
@@ -31039,7 +30760,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G546" t="inlineStr"/>
       <c r="H546" s="1" t="inlineStr"/>
       <c r="I546" s="2" t="inlineStr">
         <is>
@@ -31094,7 +30814,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G547" t="inlineStr"/>
       <c r="H547" s="1" t="inlineStr"/>
       <c r="I547" s="2" t="n"/>
       <c r="J547" s="2" t="n"/>
@@ -31150,7 +30869,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G548" t="inlineStr"/>
       <c r="H548" s="1" t="inlineStr"/>
       <c r="I548" s="2" t="inlineStr">
         <is>
@@ -31220,7 +30938,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G550" t="inlineStr"/>
       <c r="H550" s="1" t="n">
         <v>0</v>
       </c>
@@ -31277,7 +30994,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G551" t="inlineStr"/>
       <c r="H551" s="1" t="n">
         <v>0</v>
       </c>
@@ -31333,7 +31049,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G552" t="inlineStr"/>
       <c r="H552" s="1" t="n">
         <v>0</v>
       </c>
@@ -31504,7 +31219,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G555" t="inlineStr"/>
       <c r="H555" s="1" t="n">
         <v>0</v>
       </c>
@@ -31556,7 +31270,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G556" t="inlineStr"/>
       <c r="H556" s="1" t="inlineStr"/>
       <c r="I556" s="2" t="n"/>
       <c r="J556" s="2" t="n"/>
@@ -31607,7 +31320,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G557" t="inlineStr"/>
       <c r="H557" s="1" t="n">
         <v>0</v>
       </c>
@@ -31654,7 +31366,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G558" t="inlineStr"/>
       <c r="H558" s="1" t="inlineStr"/>
       <c r="I558" s="2" t="inlineStr">
         <is>
@@ -31709,7 +31420,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G559" t="inlineStr"/>
       <c r="H559" s="1" t="inlineStr"/>
       <c r="I559" s="2" t="n"/>
       <c r="J559" s="2" t="n"/>
@@ -31765,7 +31475,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G560" t="inlineStr"/>
       <c r="H560" s="1" t="n">
         <v>0</v>
       </c>
@@ -31821,7 +31530,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G561" t="inlineStr"/>
       <c r="H561" s="1" t="inlineStr"/>
       <c r="I561" s="2" t="n"/>
       <c r="J561" s="2" t="n"/>
@@ -31872,7 +31580,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G562" t="inlineStr"/>
       <c r="H562" s="1" t="n">
         <v>0</v>
       </c>
@@ -31975,7 +31682,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G564" t="inlineStr"/>
       <c r="H564" s="1" t="inlineStr"/>
       <c r="I564" s="2" t="inlineStr">
         <is>
@@ -32035,7 +31741,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G565" t="inlineStr"/>
       <c r="H565" s="1" t="inlineStr"/>
       <c r="I565" s="2" t="inlineStr">
         <is>
@@ -32155,7 +31860,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G567" t="inlineStr"/>
       <c r="H567" s="1" t="inlineStr"/>
       <c r="I567" s="2" t="inlineStr">
         <is>
@@ -32260,7 +31964,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G569" t="inlineStr"/>
       <c r="H569" s="1" t="n">
         <v>0</v>
       </c>
@@ -32316,7 +32019,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G570" t="inlineStr"/>
       <c r="H570" s="1" t="n">
         <v>0</v>
       </c>
@@ -32373,7 +32075,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G571" t="inlineStr"/>
       <c r="H571" s="1" t="inlineStr"/>
       <c r="I571" s="2" t="n"/>
       <c r="J571" s="2" t="n"/>
@@ -32424,7 +32125,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G572" t="inlineStr"/>
       <c r="H572" s="1" t="n">
         <v>0</v>
       </c>
@@ -32480,7 +32180,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G573" t="inlineStr"/>
       <c r="H573" s="1" t="inlineStr"/>
       <c r="I573" s="2" t="inlineStr">
         <is>
@@ -32540,7 +32239,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G574" t="inlineStr"/>
       <c r="H574" s="1" t="n">
         <v>0</v>
       </c>
@@ -32643,7 +32341,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G576" t="inlineStr"/>
       <c r="H576" s="1" t="inlineStr"/>
       <c r="I576" s="2" t="inlineStr">
         <is>
@@ -32750,7 +32447,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G578" t="inlineStr"/>
       <c r="H578" s="1" t="n">
         <v>0</v>
       </c>
@@ -32806,9 +32502,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G579" t="inlineStr"/>
       <c r="H579" s="1" t="inlineStr"/>
-      <c r="I579" s="2" t="n"/>
+      <c r="I579" s="2" t="inlineStr">
+        <is>
+          <t>847294009544</t>
+        </is>
+      </c>
       <c r="J579" s="2" t="n"/>
       <c r="K579" s="2" t="inlineStr"/>
       <c r="L579" s="2" t="inlineStr">
@@ -32857,7 +32556,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G580" t="inlineStr"/>
       <c r="H580" s="1" t="n">
         <v>0</v>
       </c>
@@ -32904,7 +32602,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G581" t="inlineStr"/>
       <c r="H581" s="1" t="n">
         <v>0</v>
       </c>
@@ -33016,7 +32713,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G583" t="inlineStr"/>
       <c r="H583" s="1" t="n">
         <v>0</v>
       </c>
@@ -33072,7 +32768,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G584" t="inlineStr"/>
       <c r="H584" s="1" t="n">
         <v>0</v>
       </c>
@@ -33124,7 +32819,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G585" t="inlineStr"/>
       <c r="H585" s="1" t="inlineStr"/>
       <c r="I585" s="2" t="n"/>
       <c r="J585" s="2" t="n"/>
@@ -33175,7 +32869,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G586" t="inlineStr"/>
       <c r="H586" s="1" t="n">
         <v>0</v>
       </c>
@@ -33231,7 +32924,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G587" t="inlineStr"/>
       <c r="H587" s="1" t="inlineStr"/>
       <c r="I587" s="2" t="n"/>
       <c r="J587" s="2" t="n"/>
@@ -33287,7 +32979,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G588" t="inlineStr"/>
       <c r="H588" s="1" t="inlineStr"/>
       <c r="I588" s="2" t="inlineStr">
         <is>
@@ -33342,7 +33033,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G589" t="inlineStr"/>
       <c r="H589" s="1" t="n">
         <v>0</v>
       </c>
@@ -33389,7 +33079,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G590" t="inlineStr"/>
       <c r="H590" s="1" t="inlineStr"/>
       <c r="I590" s="2" t="n"/>
       <c r="J590" s="2" t="n"/>
@@ -33445,7 +33134,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G591" t="inlineStr"/>
       <c r="H591" s="1" t="inlineStr"/>
       <c r="I591" s="2" t="inlineStr">
         <is>
@@ -33495,7 +33183,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G592" t="inlineStr"/>
       <c r="H592" s="1" t="n">
         <v>0</v>
       </c>
@@ -33547,7 +33234,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G593" t="inlineStr"/>
       <c r="H593" s="1" t="n">
         <v>0</v>
       </c>
@@ -33594,7 +33280,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G594" t="inlineStr"/>
       <c r="H594" s="1" t="n">
         <v>0</v>
       </c>
@@ -33706,7 +33391,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G596" t="inlineStr"/>
       <c r="H596" s="1" t="inlineStr"/>
       <c r="I596" s="2" t="inlineStr">
         <is>
@@ -33763,7 +33447,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G597" t="inlineStr"/>
       <c r="H597" s="1" t="inlineStr"/>
       <c r="I597" s="2" t="inlineStr">
         <is>
@@ -33818,7 +33501,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G598" t="inlineStr"/>
       <c r="H598" s="1" t="n">
         <v>0</v>
       </c>
@@ -33874,7 +33556,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G599" t="inlineStr"/>
       <c r="H599" s="1" t="n">
         <v>0</v>
       </c>
@@ -34032,7 +33713,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G602" t="inlineStr"/>
       <c r="H602" s="1" t="inlineStr"/>
       <c r="I602" s="2" t="n"/>
       <c r="J602" s="2" t="n"/>
@@ -34143,7 +33823,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G604" t="inlineStr"/>
       <c r="H604" s="1" t="n">
         <v>0</v>
       </c>
@@ -34255,7 +33934,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G606" t="inlineStr"/>
       <c r="H606" s="1" t="n">
         <v>0</v>
       </c>
@@ -34302,7 +33980,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G607" t="inlineStr"/>
       <c r="H607" s="1" t="n">
         <v>0</v>
       </c>
@@ -34358,7 +34035,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G608" t="inlineStr"/>
       <c r="H608" s="1" t="inlineStr"/>
       <c r="I608" s="2" t="inlineStr">
         <is>
@@ -34428,7 +34104,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G610" t="inlineStr"/>
       <c r="H610" s="1" t="n">
         <v>0</v>
       </c>
@@ -34484,7 +34159,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G611" t="inlineStr"/>
       <c r="H611" s="1" t="inlineStr"/>
       <c r="I611" s="2" t="inlineStr">
         <is>
@@ -34534,7 +34208,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G612" t="inlineStr"/>
       <c r="H612" s="1" t="inlineStr"/>
       <c r="I612" s="2" t="n"/>
       <c r="J612" s="2" t="n"/>
@@ -34585,7 +34258,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G613" t="inlineStr"/>
       <c r="H613" s="1" t="inlineStr"/>
       <c r="I613" s="2" t="inlineStr">
         <is>
@@ -34640,7 +34312,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G614" t="inlineStr"/>
       <c r="H614" s="1" t="n">
         <v>0</v>
       </c>
@@ -34697,7 +34368,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G615" t="inlineStr"/>
       <c r="H615" s="1" t="n">
         <v>0</v>
       </c>
@@ -34753,7 +34423,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G616" t="inlineStr"/>
       <c r="H616" s="1" t="n">
         <v>0</v>
       </c>
@@ -34809,7 +34478,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G617" t="inlineStr"/>
       <c r="H617" s="1" t="n">
         <v>0</v>
       </c>
@@ -34935,7 +34603,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G620" t="inlineStr"/>
       <c r="H620" s="1" t="n">
         <v>0</v>
       </c>
@@ -34992,7 +34659,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G621" t="inlineStr"/>
       <c r="H621" s="1" t="n">
         <v>0</v>
       </c>
@@ -35048,7 +34714,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G622" t="inlineStr"/>
       <c r="H622" s="1" t="n">
         <v>0</v>
       </c>
@@ -35215,7 +34880,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G625" t="inlineStr"/>
       <c r="H625" s="1" t="n">
         <v>0</v>
       </c>
@@ -35272,7 +34936,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G626" t="inlineStr"/>
       <c r="H626" s="1" t="n">
         <v>3.99</v>
       </c>
@@ -35334,7 +34997,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G627" t="inlineStr"/>
       <c r="H627" s="1" t="n">
         <v>0</v>
       </c>
@@ -35447,9 +35109,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G629" t="inlineStr"/>
       <c r="H629" s="1" t="inlineStr"/>
-      <c r="I629" s="2" t="n"/>
+      <c r="I629" s="2" t="inlineStr">
+        <is>
+          <t>729205001796</t>
+        </is>
+      </c>
       <c r="J629" s="2" t="n"/>
       <c r="K629" s="2" t="inlineStr"/>
       <c r="L629" s="2" t="inlineStr">
@@ -35498,7 +35163,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G630" t="inlineStr"/>
       <c r="H630" s="1" t="n">
         <v>0</v>
       </c>
@@ -35557,7 +35221,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G631" t="inlineStr"/>
       <c r="H631" s="1" t="n">
         <v>0</v>
       </c>
@@ -35664,9 +35327,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G633" t="inlineStr"/>
       <c r="H633" s="1" t="inlineStr"/>
-      <c r="I633" s="2" t="n"/>
+      <c r="I633" s="2" t="inlineStr">
+        <is>
+          <t>847294003092</t>
+        </is>
+      </c>
       <c r="J633" s="2" t="n"/>
       <c r="K633" s="2" t="inlineStr"/>
       <c r="L633" s="2" t="inlineStr">
@@ -35720,7 +35386,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G634" t="inlineStr"/>
       <c r="H634" s="1" t="n">
         <v>0</v>
       </c>
@@ -35777,7 +35442,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G635" t="inlineStr"/>
       <c r="H635" s="1" t="n">
         <v>0</v>
       </c>
@@ -35834,7 +35498,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G636" t="inlineStr"/>
       <c r="H636" s="1" t="n">
         <v>0</v>
       </c>
@@ -35890,7 +35553,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G637" t="inlineStr"/>
       <c r="H637" s="1" t="n">
         <v>0</v>
       </c>
@@ -35946,7 +35608,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G638" t="inlineStr"/>
       <c r="H638" s="1" t="n">
         <v>0</v>
       </c>
@@ -36002,9 +35663,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G639" t="inlineStr"/>
       <c r="H639" s="1" t="inlineStr"/>
-      <c r="I639" s="2" t="n"/>
+      <c r="I639" s="2" t="inlineStr">
+        <is>
+          <t>729205258886</t>
+        </is>
+      </c>
       <c r="J639" s="2" t="n"/>
       <c r="K639" s="2" t="inlineStr"/>
       <c r="L639" s="2" t="inlineStr">
@@ -36053,7 +35717,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G640" t="inlineStr"/>
       <c r="H640" s="1" t="n">
         <v>0</v>
       </c>
@@ -36165,7 +35828,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G642" t="inlineStr"/>
       <c r="H642" s="1" t="n">
         <v>0</v>
       </c>
@@ -36272,7 +35934,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G644" t="inlineStr"/>
       <c r="H644" s="1" t="n">
         <v>0</v>
       </c>
@@ -36324,7 +35985,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G645" t="inlineStr"/>
       <c r="H645" s="1" t="inlineStr"/>
       <c r="I645" s="2" t="inlineStr">
         <is>
@@ -36379,7 +36039,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G647" t="inlineStr"/>
       <c r="H647" s="1" t="inlineStr"/>
       <c r="I647" s="2" t="inlineStr">
         <is>
@@ -36429,7 +36088,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G648" t="inlineStr"/>
       <c r="H648" s="1" t="n">
         <v>0</v>
       </c>
@@ -36480,7 +36138,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G649" t="inlineStr"/>
       <c r="H649" s="1" t="n">
         <v>0</v>
       </c>
@@ -36532,7 +36189,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G650" t="inlineStr"/>
       <c r="H650" s="1" t="n">
         <v>0</v>
       </c>
@@ -36584,7 +36240,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G651" t="inlineStr"/>
       <c r="H651" s="1" t="n">
         <v>0</v>
       </c>
@@ -36640,7 +36295,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G652" t="inlineStr"/>
       <c r="H652" s="1" t="n">
         <v>0</v>
       </c>
@@ -36696,7 +36350,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G653" t="inlineStr"/>
       <c r="H653" s="1" t="n">
         <v>0</v>
       </c>
@@ -36752,7 +36405,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G654" t="inlineStr"/>
       <c r="H654" s="1" t="n">
         <v>0</v>
       </c>
@@ -36808,7 +36460,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G655" t="inlineStr"/>
       <c r="H655" s="1" t="n">
         <v>0</v>
       </c>
@@ -36865,7 +36516,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G657" t="inlineStr"/>
       <c r="H657" s="1" t="n">
         <v>0</v>
       </c>
@@ -36924,7 +36574,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G658" t="inlineStr"/>
       <c r="H658" s="1" t="inlineStr"/>
       <c r="I658" s="2" t="inlineStr">
         <is>
@@ -36976,7 +36625,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G659" t="inlineStr"/>
       <c r="H659" s="1" t="inlineStr"/>
       <c r="I659" s="2" t="inlineStr">
         <is>
@@ -37036,7 +36684,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G660" t="inlineStr"/>
       <c r="H660" s="1" t="n">
         <v>0</v>
       </c>
@@ -37092,7 +36739,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G661" t="inlineStr"/>
       <c r="H661" s="1" t="n">
         <v>0</v>
       </c>
@@ -37144,7 +36790,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G662" t="inlineStr"/>
       <c r="H662" s="1" t="n">
         <v>0</v>
       </c>
@@ -37208,9 +36853,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G663" t="inlineStr"/>
       <c r="H663" s="1" t="inlineStr"/>
-      <c r="I663" s="2" t="n"/>
+      <c r="I663" s="2" t="inlineStr">
+        <is>
+          <t>847294016344</t>
+        </is>
+      </c>
       <c r="J663" s="2" t="n"/>
       <c r="K663" s="2" t="inlineStr"/>
       <c r="L663" s="2" t="inlineStr">
@@ -37264,7 +36912,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G664" t="inlineStr"/>
       <c r="H664" s="1" t="inlineStr"/>
       <c r="I664" s="2" t="inlineStr">
         <is>
@@ -37319,7 +36966,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G665" t="inlineStr"/>
       <c r="H665" s="1" t="inlineStr"/>
       <c r="I665" s="2" t="inlineStr">
         <is>
@@ -37439,7 +37085,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G667" t="inlineStr"/>
       <c r="H667" s="1" t="n">
         <v>0</v>
       </c>
@@ -37486,7 +37131,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G668" t="inlineStr"/>
       <c r="H668" s="1" t="inlineStr"/>
       <c r="I668" s="2" t="inlineStr">
         <is>
@@ -37597,7 +37241,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G670" t="inlineStr"/>
       <c r="H670" s="1" t="n">
         <v>0</v>
       </c>
@@ -37653,7 +37296,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G671" t="inlineStr"/>
       <c r="H671" s="1" t="n">
         <v>0</v>
       </c>
@@ -37709,7 +37351,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G672" t="inlineStr"/>
       <c r="H672" s="1" t="n">
         <v>0</v>
       </c>
@@ -37756,7 +37397,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G673" t="inlineStr"/>
       <c r="H673" s="1" t="n">
         <v>0</v>
       </c>
@@ -37803,7 +37443,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G674" t="inlineStr"/>
       <c r="H674" s="1" t="n">
         <v>0</v>
       </c>
@@ -37860,7 +37499,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G675" t="inlineStr"/>
       <c r="H675" s="1" t="n">
         <v>0</v>
       </c>
@@ -37907,7 +37545,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G676" t="inlineStr"/>
       <c r="H676" s="1" t="inlineStr"/>
       <c r="I676" s="2" t="inlineStr">
         <is>
@@ -37967,7 +37604,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G677" t="inlineStr"/>
       <c r="H677" s="1" t="n">
         <v>0</v>
       </c>
@@ -38018,6 +37654,11 @@
           <t>Fixed</t>
         </is>
       </c>
+      <c r="I678" s="2" t="inlineStr">
+        <is>
+          <t>601527770171</t>
+        </is>
+      </c>
       <c r="L678" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -38061,7 +37702,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G679" t="inlineStr"/>
       <c r="H679" s="1" t="inlineStr"/>
       <c r="I679" s="2" t="n"/>
       <c r="J679" s="2" t="n"/>
@@ -38117,7 +37757,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G680" t="inlineStr"/>
       <c r="H680" s="1" t="inlineStr"/>
       <c r="I680" s="2" t="n"/>
       <c r="J680" s="2" t="n"/>
@@ -38173,7 +37812,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G681" t="inlineStr"/>
       <c r="H681" s="1" t="inlineStr"/>
       <c r="I681" s="45" t="n">
         <v>690250430599</v>
@@ -38251,7 +37889,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G684" t="inlineStr"/>
       <c r="H684" s="1" t="inlineStr"/>
       <c r="I684" s="2" t="inlineStr">
         <is>
@@ -38356,9 +37993,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G686" t="inlineStr"/>
       <c r="H686" s="1" t="inlineStr"/>
-      <c r="I686" s="2" t="n"/>
+      <c r="I686" s="2" t="inlineStr">
+        <is>
+          <t>729205065866</t>
+        </is>
+      </c>
       <c r="J686" s="2" t="n"/>
       <c r="K686" s="2" t="inlineStr"/>
       <c r="L686" s="2" t="inlineStr">
@@ -38412,7 +38052,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G687" t="inlineStr"/>
       <c r="H687" s="1" t="n">
         <v>0</v>
       </c>
@@ -38519,9 +38158,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G689" t="inlineStr"/>
       <c r="H689" s="1" t="inlineStr"/>
-      <c r="I689" s="2" t="n"/>
+      <c r="I689" s="2" t="inlineStr">
+        <is>
+          <t>847294017228</t>
+        </is>
+      </c>
       <c r="J689" s="2" t="n"/>
       <c r="K689" s="2" t="inlineStr"/>
       <c r="L689" s="2" t="inlineStr">
@@ -38635,7 +38277,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G691" t="inlineStr"/>
       <c r="H691" s="1" t="n">
         <v>0</v>
       </c>
@@ -38691,7 +38332,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G692" t="inlineStr"/>
       <c r="H692" s="1" t="n">
         <v>0</v>
       </c>
@@ -38738,7 +38378,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G693" t="inlineStr"/>
       <c r="H693" s="1" t="inlineStr"/>
       <c r="I693" s="2" t="inlineStr">
         <is>
@@ -38853,7 +38492,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G695" t="inlineStr"/>
       <c r="H695" s="1" t="n">
         <v>0</v>
       </c>
@@ -38960,7 +38598,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G697" t="inlineStr"/>
       <c r="H697" s="1" t="inlineStr"/>
       <c r="I697" s="2" t="inlineStr">
         <is>
@@ -39020,7 +38657,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G698" t="inlineStr"/>
       <c r="H698" s="1" t="inlineStr"/>
       <c r="I698" s="2" t="inlineStr">
         <is>
@@ -39065,7 +38701,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G699" t="inlineStr"/>
       <c r="H699" s="1" t="n">
         <v>0</v>
       </c>
@@ -39119,7 +38754,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G700" t="inlineStr"/>
       <c r="H700" s="1" t="inlineStr"/>
       <c r="I700" s="2" t="inlineStr">
         <is>
@@ -39184,7 +38818,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G702" t="inlineStr"/>
       <c r="H702" s="1" t="inlineStr"/>
       <c r="I702" s="2" t="inlineStr">
         <is>
@@ -39304,7 +38937,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G704" t="inlineStr"/>
       <c r="H704" s="1" t="inlineStr"/>
       <c r="I704" s="2" t="inlineStr">
         <is>
@@ -39374,7 +39006,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G706" t="inlineStr"/>
       <c r="H706" s="1" t="inlineStr"/>
       <c r="I706" s="2" t="n"/>
       <c r="J706" s="2" t="n"/>
@@ -39430,7 +39061,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G707" t="inlineStr"/>
       <c r="H707" s="1" t="n">
         <v>0</v>
       </c>
@@ -39477,7 +39107,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G708" t="inlineStr"/>
       <c r="H708" s="1" t="inlineStr"/>
       <c r="I708" s="2" t="n"/>
       <c r="J708" s="2" t="n"/>
@@ -39528,7 +39157,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G709" t="inlineStr"/>
       <c r="H709" s="1" t="inlineStr"/>
       <c r="I709" s="2" t="inlineStr">
         <is>
@@ -39578,7 +39206,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G710" t="inlineStr"/>
       <c r="H710" s="1" t="n">
         <v>0</v>
       </c>
@@ -39696,7 +39323,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G712" t="inlineStr"/>
       <c r="H712" s="1" t="n">
         <v>0</v>
       </c>
@@ -39748,7 +39374,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G713" t="inlineStr"/>
       <c r="H713" s="1" t="inlineStr"/>
       <c r="I713" s="2" t="inlineStr">
         <is>
@@ -39803,7 +39428,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G714" t="inlineStr"/>
       <c r="H714" s="1" t="inlineStr"/>
       <c r="I714" s="2" t="inlineStr">
         <is>
@@ -39863,7 +39487,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G715" t="inlineStr"/>
       <c r="H715" s="1" t="inlineStr"/>
       <c r="I715" s="2" t="inlineStr">
         <is>
@@ -39913,7 +39536,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G716" t="inlineStr"/>
       <c r="H716" s="1" t="inlineStr"/>
       <c r="I716" s="2" t="inlineStr">
         <is>
@@ -40083,7 +39705,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G719" t="inlineStr"/>
       <c r="H719" s="1" t="inlineStr"/>
       <c r="I719" s="2" t="inlineStr">
         <is>
@@ -40143,7 +39764,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G720" t="inlineStr"/>
       <c r="H720" s="1" t="inlineStr"/>
       <c r="I720" s="2" t="inlineStr">
         <is>
@@ -40378,7 +39998,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G724" t="inlineStr"/>
       <c r="H724" s="1" t="n">
         <v>0</v>
       </c>
@@ -40435,7 +40054,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G725" t="inlineStr"/>
       <c r="H725" s="1" t="n">
         <v>0</v>
       </c>
@@ -40491,7 +40109,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G726" t="inlineStr"/>
       <c r="H726" s="1" t="inlineStr"/>
       <c r="I726" s="2" t="inlineStr">
         <is>
@@ -40654,7 +40271,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G729" t="inlineStr"/>
       <c r="H729" s="1" t="n">
         <v>0</v>
       </c>
@@ -40705,7 +40321,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G730" t="inlineStr"/>
       <c r="H730" s="1" t="n">
         <v>0</v>
       </c>
@@ -40761,7 +40376,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G731" t="inlineStr"/>
       <c r="H731" s="1" t="inlineStr"/>
       <c r="I731" s="2" t="inlineStr">
         <is>
@@ -40816,7 +40430,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G732" t="inlineStr"/>
       <c r="H732" s="1" t="inlineStr"/>
       <c r="I732" s="2" t="n"/>
       <c r="J732" s="2" t="n"/>
@@ -40932,7 +40545,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G734" t="inlineStr"/>
       <c r="H734" s="1" t="inlineStr"/>
       <c r="I734" s="2" t="inlineStr">
         <is>
@@ -41052,7 +40664,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G736" t="inlineStr"/>
       <c r="H736" s="1" t="n">
         <v>0</v>
       </c>
@@ -41111,7 +40722,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G737" t="inlineStr"/>
       <c r="H737" s="1" t="inlineStr"/>
       <c r="I737" s="2" t="n"/>
       <c r="J737" s="2" t="n"/>
@@ -41222,7 +40832,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G739" t="inlineStr"/>
       <c r="H739" s="1" t="n">
         <v>0</v>
       </c>
@@ -41280,7 +40889,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G740" t="inlineStr"/>
       <c r="H740" s="1" t="n">
         <v>0</v>
       </c>
@@ -41339,7 +40947,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G742" t="inlineStr"/>
       <c r="H742" s="1" t="n">
         <v>0</v>
       </c>
@@ -41395,7 +41002,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G743" t="inlineStr"/>
       <c r="H743" s="1" t="inlineStr"/>
       <c r="I743" s="2" t="inlineStr">
         <is>
@@ -41511,7 +41117,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G746" t="inlineStr"/>
       <c r="H746" s="1" t="n">
         <v>0</v>
       </c>
@@ -41558,7 +41163,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G747" t="inlineStr"/>
       <c r="H747" s="1" t="n">
         <v>0</v>
       </c>
@@ -41604,7 +41208,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G748" t="inlineStr"/>
       <c r="H748" s="1" t="n">
         <v>0</v>
       </c>
@@ -41651,7 +41254,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G749" t="inlineStr"/>
       <c r="H749" s="1" t="n">
         <v>0</v>
       </c>
@@ -41703,9 +41305,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G750" t="inlineStr"/>
       <c r="H750" s="1" t="inlineStr"/>
-      <c r="I750" s="2" t="n"/>
+      <c r="I750" s="2" t="inlineStr">
+        <is>
+          <t>847294020433</t>
+        </is>
+      </c>
       <c r="J750" s="2" t="n"/>
       <c r="K750" s="2" t="inlineStr"/>
       <c r="L750" s="2" t="inlineStr">
@@ -41754,7 +41359,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G751" t="inlineStr"/>
       <c r="H751" s="1" t="n">
         <v>0</v>
       </c>
@@ -41866,7 +41470,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G753" t="inlineStr"/>
       <c r="H753" s="1" t="inlineStr"/>
       <c r="I753" s="2" t="inlineStr">
         <is>
@@ -41921,7 +41524,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G754" t="inlineStr"/>
       <c r="H754" s="1" t="n">
         <v>0</v>
       </c>
@@ -41977,7 +41579,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G755" t="inlineStr"/>
       <c r="H755" s="1" t="n">
         <v>0</v>
       </c>
@@ -42034,7 +41635,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G756" t="inlineStr"/>
       <c r="H756" s="1" t="n">
         <v>0</v>
       </c>
@@ -42143,7 +41743,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G758" t="inlineStr"/>
       <c r="H758" s="1" t="n">
         <v>0</v>
       </c>
@@ -42199,7 +41798,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G759" t="inlineStr"/>
       <c r="H759" s="1" t="n">
         <v>0</v>
       </c>
@@ -42246,7 +41844,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G760" t="inlineStr"/>
       <c r="H760" s="1" t="inlineStr"/>
       <c r="I760" s="2" t="n"/>
       <c r="J760" s="2" t="n"/>
@@ -42297,7 +41894,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G761" t="inlineStr"/>
       <c r="H761" s="1" t="n">
         <v>0</v>
       </c>
@@ -42353,7 +41949,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G762" t="inlineStr"/>
       <c r="H762" s="1" t="n">
         <v>0</v>
       </c>
@@ -42405,7 +42000,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G763" t="inlineStr"/>
       <c r="H763" s="1" t="n">
         <v>0</v>
       </c>
@@ -42461,7 +42055,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G764" t="inlineStr"/>
       <c r="H764" s="1" t="n">
         <v>0</v>
       </c>
@@ -42564,7 +42157,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G766" t="inlineStr"/>
       <c r="H766" s="1" t="inlineStr"/>
       <c r="I766" s="2" t="n"/>
       <c r="J766" s="2" t="n"/>
@@ -42680,7 +42272,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G768" t="inlineStr"/>
       <c r="H768" s="1" t="inlineStr"/>
       <c r="I768" s="2" t="inlineStr">
         <is>
@@ -42811,7 +42402,11 @@
       <c r="H770" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I770" s="2" t="n"/>
+      <c r="I770" s="2" t="inlineStr">
+        <is>
+          <t>847294019109</t>
+        </is>
+      </c>
       <c r="J770" s="2" t="n"/>
       <c r="K770" s="2" t="inlineStr"/>
       <c r="L770" s="2" t="inlineStr">
@@ -42915,7 +42510,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G772" t="inlineStr"/>
       <c r="H772" s="1" t="n">
         <v>0</v>
       </c>
@@ -42962,7 +42556,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G773" t="inlineStr"/>
       <c r="H773" s="1" t="n">
         <v>0</v>
       </c>
@@ -43060,9 +42653,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G775" t="inlineStr"/>
       <c r="H775" s="1" t="inlineStr"/>
-      <c r="I775" s="2" t="n"/>
+      <c r="I775" s="2" t="inlineStr">
+        <is>
+          <t>847294031798</t>
+        </is>
+      </c>
       <c r="J775" s="2" t="n"/>
       <c r="K775" s="2" t="inlineStr"/>
       <c r="L775" s="2" t="inlineStr">
@@ -43116,7 +42712,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G776" t="inlineStr"/>
       <c r="H776" s="1" t="inlineStr"/>
       <c r="I776" s="2" t="inlineStr">
         <is>
@@ -43176,7 +42771,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G777" t="inlineStr"/>
       <c r="H777" s="1" t="n">
         <v>0</v>
       </c>
@@ -43283,7 +42877,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G779" t="inlineStr"/>
       <c r="H779" s="1" t="inlineStr"/>
       <c r="I779" s="2" t="inlineStr">
         <is>
@@ -43338,7 +42931,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G780" t="inlineStr"/>
       <c r="H780" s="1" t="inlineStr"/>
       <c r="I780" s="2" t="inlineStr">
         <is>
@@ -43398,7 +42990,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G781" t="inlineStr"/>
       <c r="H781" s="1" t="inlineStr"/>
       <c r="I781" s="2" t="inlineStr">
         <is>
@@ -43448,7 +43039,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G782" t="inlineStr"/>
       <c r="H782" s="1" t="inlineStr"/>
       <c r="I782" s="2" t="inlineStr">
         <is>
@@ -43508,7 +43098,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G783" t="inlineStr"/>
       <c r="H783" s="1" t="n">
         <v>0</v>
       </c>
@@ -43615,7 +43204,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G785" t="inlineStr"/>
       <c r="H785" s="1" t="inlineStr"/>
       <c r="I785" s="2" t="n"/>
       <c r="J785" s="2" t="n"/>
@@ -43731,7 +43319,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G787" t="inlineStr"/>
       <c r="H787" s="1" t="inlineStr"/>
       <c r="I787" s="2" t="inlineStr">
         <is>
@@ -43786,7 +43373,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G788" t="inlineStr"/>
       <c r="H788" s="1" t="n">
         <v>0</v>
       </c>
@@ -43896,7 +43482,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G790" t="inlineStr"/>
       <c r="H790" s="1" t="n">
         <v>0</v>
       </c>
@@ -43948,7 +43533,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G791" t="inlineStr"/>
       <c r="H791" s="1" t="n">
         <v>0</v>
       </c>
@@ -44004,7 +43588,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G792" t="inlineStr"/>
       <c r="H792" s="1" t="n">
         <v>0</v>
       </c>
@@ -44051,7 +43634,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G793" t="inlineStr"/>
       <c r="H793" s="1" t="n">
         <v>0</v>
       </c>
@@ -44167,7 +43749,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G795" t="inlineStr"/>
       <c r="H795" s="1" t="n">
         <v>0</v>
       </c>
@@ -44234,7 +43815,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G798" t="inlineStr"/>
       <c r="H798" s="1" t="inlineStr"/>
       <c r="I798" s="2" t="inlineStr">
         <is>
@@ -44314,7 +43894,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G801" t="inlineStr"/>
       <c r="H801" s="1" t="n">
         <v>0</v>
       </c>
@@ -44370,9 +43949,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G802" t="inlineStr"/>
       <c r="H802" s="1" t="inlineStr"/>
-      <c r="I802" s="2" t="n"/>
+      <c r="I802" s="2" t="inlineStr">
+        <is>
+          <t>847294025391</t>
+        </is>
+      </c>
       <c r="J802" s="2" t="n"/>
       <c r="K802" s="2" t="inlineStr"/>
       <c r="L802" s="2" t="inlineStr">
@@ -44476,7 +44058,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G804" t="inlineStr"/>
       <c r="H804" s="1" t="inlineStr"/>
       <c r="I804" s="2" t="inlineStr">
         <is>
@@ -44606,7 +44187,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G807" t="inlineStr"/>
       <c r="H807" s="1" t="n">
         <v>0</v>
       </c>
@@ -44653,7 +44233,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G808" t="inlineStr"/>
       <c r="H808" s="1" t="n">
         <v>0</v>
       </c>
@@ -44700,7 +44279,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G809" t="inlineStr"/>
       <c r="H809" s="1" t="inlineStr"/>
       <c r="I809" s="2" t="inlineStr">
         <is>
@@ -44755,9 +44333,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G810" t="inlineStr"/>
       <c r="H810" s="1" t="inlineStr"/>
-      <c r="I810" s="2" t="n"/>
+      <c r="I810" s="2" t="inlineStr">
+        <is>
+          <t>847294041445</t>
+        </is>
+      </c>
       <c r="J810" s="2" t="n"/>
       <c r="K810" s="2" t="inlineStr"/>
       <c r="L810" s="2" t="inlineStr">
@@ -44866,7 +44447,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G812" t="inlineStr"/>
       <c r="H812" s="1" t="n">
         <v>0</v>
       </c>
@@ -44913,7 +44493,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G813" t="inlineStr"/>
       <c r="H813" s="1" t="inlineStr"/>
       <c r="I813" s="2" t="n"/>
       <c r="J813" s="2" t="n"/>
@@ -44974,7 +44553,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G815" t="inlineStr"/>
       <c r="H815" s="1" t="n">
         <v>0</v>
       </c>
@@ -45030,7 +44608,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G816" t="inlineStr"/>
       <c r="H816" s="1" t="inlineStr"/>
       <c r="I816" s="2" t="inlineStr">
         <is>
@@ -45145,7 +44722,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G818" t="inlineStr"/>
       <c r="H818" s="1" t="inlineStr"/>
       <c r="I818" s="2" t="inlineStr">
         <is>
@@ -45200,7 +44776,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G819" t="inlineStr"/>
       <c r="H819" s="1" t="inlineStr"/>
       <c r="I819" s="2" t="n"/>
       <c r="J819" s="2" t="n"/>
@@ -45256,9 +44831,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G820" t="inlineStr"/>
       <c r="H820" s="1" t="inlineStr"/>
-      <c r="I820" s="2" t="n"/>
+      <c r="I820" s="2" t="inlineStr">
+        <is>
+          <t>676821334831</t>
+        </is>
+      </c>
       <c r="J820" s="2" t="n"/>
       <c r="K820" s="2" t="inlineStr"/>
       <c r="L820" s="2" t="inlineStr">
@@ -45307,7 +44885,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G821" t="inlineStr"/>
       <c r="H821" s="1" t="n">
         <v>0</v>
       </c>
@@ -45354,7 +44931,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G822" t="inlineStr"/>
       <c r="H822" s="1" t="n">
         <v>0</v>
       </c>
@@ -45461,7 +45037,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G824" t="inlineStr"/>
       <c r="H824" s="1" t="n">
         <v>0</v>
       </c>
@@ -45508,7 +45083,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G825" t="inlineStr"/>
       <c r="H825" s="1" t="inlineStr"/>
       <c r="I825" s="2" t="inlineStr">
         <is>
@@ -45563,7 +45137,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G826" t="inlineStr"/>
       <c r="H826" s="1" t="n">
         <v>0</v>
       </c>
@@ -45670,7 +45243,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G828" t="inlineStr"/>
       <c r="H828" s="1" t="n">
         <v>0</v>
       </c>
@@ -45734,7 +45306,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G829" t="inlineStr"/>
       <c r="H829" s="1" t="inlineStr"/>
       <c r="I829" s="2" t="n"/>
       <c r="J829" s="2" t="n"/>
@@ -45790,7 +45361,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G830" t="inlineStr"/>
       <c r="H830" s="1" t="n">
         <v>0</v>
       </c>
@@ -45888,7 +45458,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G832" t="inlineStr"/>
       <c r="H832" s="1" t="inlineStr"/>
       <c r="I832" s="2" t="n"/>
       <c r="J832" s="2" t="n"/>
@@ -45944,9 +45513,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G833" t="inlineStr"/>
       <c r="H833" s="1" t="inlineStr"/>
-      <c r="I833" s="2" t="n"/>
+      <c r="I833" s="2" t="inlineStr">
+        <is>
+          <t>847294093413</t>
+        </is>
+      </c>
       <c r="J833" s="2" t="n"/>
       <c r="K833" s="2" t="inlineStr"/>
       <c r="L833" s="2" t="inlineStr">
@@ -45995,7 +45567,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G834" t="inlineStr"/>
       <c r="H834" s="1" t="n">
         <v>0</v>
       </c>
@@ -46042,7 +45613,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G835" t="inlineStr"/>
       <c r="H835" s="1" t="inlineStr"/>
       <c r="I835" s="2" t="inlineStr">
         <is>
@@ -46102,7 +45672,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G836" t="inlineStr"/>
       <c r="H836" s="1" t="n">
         <v>0</v>
       </c>
@@ -46153,7 +45722,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G837" t="inlineStr"/>
       <c r="H837" s="1" t="inlineStr"/>
       <c r="I837" s="2" t="inlineStr">
         <is>
@@ -46210,7 +45778,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G838" t="inlineStr"/>
       <c r="H838" s="1" t="n">
         <v>0</v>
       </c>
@@ -46266,7 +45833,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G839" t="inlineStr"/>
       <c r="H839" s="1" t="inlineStr"/>
       <c r="I839" s="2" t="inlineStr">
         <is>
@@ -46321,7 +45887,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G840" t="inlineStr"/>
       <c r="H840" s="1" t="inlineStr"/>
       <c r="I840" s="2" t="inlineStr">
         <is>
@@ -46436,7 +46001,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G842" t="inlineStr"/>
       <c r="H842" s="1" t="n">
         <v>0</v>
       </c>
@@ -46488,7 +46052,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G843" t="inlineStr"/>
       <c r="H843" s="1" t="inlineStr"/>
       <c r="I843" s="2" t="inlineStr">
         <is>
@@ -46538,7 +46101,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G844" t="inlineStr"/>
       <c r="H844" s="1" t="inlineStr"/>
       <c r="I844" s="2" t="inlineStr">
         <is>
@@ -46708,7 +46270,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G847" t="inlineStr"/>
       <c r="H847" s="1" t="n">
         <v>0</v>
       </c>
@@ -46760,7 +46321,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G848" t="inlineStr"/>
       <c r="H848" s="1" t="inlineStr"/>
       <c r="I848" s="2" t="n"/>
       <c r="J848" s="2" t="n"/>
@@ -46811,7 +46371,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G849" t="inlineStr"/>
       <c r="H849" s="1" t="n">
         <v>0</v>
       </c>
@@ -46868,7 +46427,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G850" t="inlineStr"/>
       <c r="H850" s="1" t="inlineStr"/>
       <c r="I850" s="2" t="inlineStr">
         <is>
@@ -46925,7 +46483,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G851" t="inlineStr"/>
       <c r="H851" s="1" t="n">
         <v>0</v>
       </c>
@@ -46982,7 +46539,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G852" t="inlineStr"/>
       <c r="H852" s="1" t="inlineStr"/>
       <c r="I852" s="2" t="n"/>
       <c r="J852" s="2" t="n"/>
@@ -47038,7 +46594,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G853" t="inlineStr"/>
       <c r="H853" s="1" t="n">
         <v>0</v>
       </c>
@@ -47094,7 +46649,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G854" t="inlineStr"/>
       <c r="H854" s="1" t="n">
         <v>0</v>
       </c>
@@ -47141,7 +46695,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G855" t="inlineStr"/>
       <c r="H855" s="1" t="inlineStr"/>
       <c r="I855" s="2" t="n"/>
       <c r="J855" s="2" t="n"/>
@@ -47192,7 +46745,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G856" t="inlineStr"/>
       <c r="H856" s="1" t="n">
         <v>0</v>
       </c>
@@ -47239,7 +46791,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G857" t="inlineStr"/>
       <c r="H857" s="1" t="n">
         <v>0</v>
       </c>
@@ -47295,7 +46846,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G858" t="inlineStr"/>
       <c r="H858" s="1" t="n">
         <v>0</v>
       </c>
@@ -47344,7 +46894,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G859" t="inlineStr"/>
       <c r="H859" s="1" t="inlineStr"/>
       <c r="I859" s="2" t="inlineStr">
         <is>
@@ -47406,7 +46955,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G860" t="inlineStr"/>
       <c r="H860" s="1" t="inlineStr"/>
       <c r="I860" s="2" t="inlineStr">
         <is>
@@ -47507,7 +47055,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G862" t="inlineStr"/>
       <c r="H862" s="1" t="inlineStr"/>
       <c r="I862" s="2" t="inlineStr">
         <is>
@@ -47552,7 +47099,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G863" t="inlineStr"/>
       <c r="H863" s="1" t="inlineStr"/>
       <c r="I863" s="2" t="inlineStr">
         <is>
@@ -47612,7 +47158,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G864" t="inlineStr"/>
       <c r="H864" s="1" t="inlineStr"/>
       <c r="I864" s="2" t="inlineStr">
         <is>
@@ -47657,7 +47202,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G865" t="inlineStr"/>
       <c r="H865" s="1" t="n">
         <v>0</v>
       </c>
@@ -47713,7 +47257,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G866" t="inlineStr"/>
       <c r="H866" s="1" t="inlineStr"/>
       <c r="I866" s="2" t="n"/>
       <c r="J866" s="2" t="n"/>
@@ -47764,7 +47307,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G867" t="inlineStr"/>
       <c r="H867" s="1" t="inlineStr"/>
       <c r="I867" s="2" t="inlineStr">
         <is>
@@ -47814,7 +47356,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G868" t="inlineStr"/>
       <c r="H868" s="1" t="n">
         <v>0</v>
       </c>
@@ -47866,7 +47407,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G869" t="inlineStr"/>
       <c r="H869" s="1" t="inlineStr"/>
       <c r="I869" s="2" t="n"/>
       <c r="J869" s="2" t="n"/>
@@ -47917,7 +47457,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G870" t="inlineStr"/>
       <c r="H870" s="1" t="inlineStr"/>
       <c r="I870" s="2" t="inlineStr">
         <is>
@@ -47962,7 +47501,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G871" t="inlineStr"/>
       <c r="H871" s="1" t="n">
         <v>0</v>
       </c>
@@ -48009,7 +47547,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G872" t="inlineStr"/>
       <c r="H872" s="1" t="inlineStr"/>
       <c r="I872" s="2" t="n"/>
       <c r="J872" s="2" t="n"/>
@@ -48055,7 +47592,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G873" t="inlineStr"/>
       <c r="H873" s="1" t="n">
         <v>0</v>
       </c>
@@ -48102,7 +47638,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G874" t="inlineStr"/>
       <c r="H874" s="1" t="n">
         <v>0</v>
       </c>
@@ -48219,7 +47754,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G876" t="inlineStr"/>
       <c r="H876" s="1" t="n">
         <v>0</v>
       </c>
@@ -48271,7 +47805,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G877" t="inlineStr"/>
       <c r="H877" s="1" t="n">
         <v>0</v>
       </c>
@@ -48323,7 +47856,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G878" t="inlineStr"/>
       <c r="H878" s="1" t="inlineStr"/>
       <c r="I878" s="2" t="n"/>
       <c r="J878" s="2" t="n"/>
@@ -48434,7 +47966,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G880" t="inlineStr"/>
       <c r="H880" s="1" t="inlineStr"/>
       <c r="I880" s="2" t="n"/>
       <c r="J880" s="2" t="n"/>
@@ -48490,7 +48021,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G881" t="inlineStr"/>
       <c r="H881" s="1" t="n">
         <v>0</v>
       </c>
@@ -48546,7 +48076,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G882" t="inlineStr"/>
       <c r="H882" s="1" t="n">
         <v>0</v>
       </c>
@@ -48602,9 +48131,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G883" t="inlineStr"/>
       <c r="H883" s="1" t="inlineStr"/>
-      <c r="I883" s="2" t="n"/>
+      <c r="I883" s="2" t="inlineStr">
+        <is>
+          <t>847294088655</t>
+        </is>
+      </c>
       <c r="J883" s="2" t="n"/>
       <c r="K883" s="2" t="inlineStr"/>
       <c r="L883" s="2" t="inlineStr">
@@ -48653,7 +48185,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G884" t="inlineStr"/>
       <c r="H884" s="1" t="n">
         <v>0</v>
       </c>
@@ -48710,7 +48241,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G885" t="inlineStr"/>
       <c r="H885" s="1" t="n">
         <v>0</v>
       </c>
@@ -48767,7 +48297,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G886" t="inlineStr"/>
       <c r="H886" s="1" t="n">
         <v>0</v>
       </c>
@@ -48884,7 +48413,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G888" t="inlineStr"/>
       <c r="H888" s="1" t="n">
         <v>0</v>
       </c>
@@ -48940,7 +48468,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G889" t="inlineStr"/>
       <c r="H889" s="1" t="n">
         <v>0</v>
       </c>
@@ -49002,7 +48529,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G890" t="inlineStr"/>
       <c r="H890" s="1" t="n">
         <v>0</v>
       </c>
@@ -49105,7 +48631,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G892" t="inlineStr"/>
       <c r="H892" s="1" t="n">
         <v>0</v>
       </c>
@@ -49161,7 +48686,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G893" t="inlineStr"/>
       <c r="H893" s="1" t="n">
         <v>0</v>
       </c>
@@ -49208,7 +48732,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G894" t="inlineStr"/>
       <c r="H894" s="1" t="inlineStr"/>
       <c r="I894" s="2" t="n"/>
       <c r="J894" s="2" t="n"/>
@@ -49259,9 +48782,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G895" t="inlineStr"/>
       <c r="H895" s="1" t="inlineStr"/>
-      <c r="I895" s="2" t="n"/>
+      <c r="I895" s="2" t="inlineStr">
+        <is>
+          <t>676821075789</t>
+        </is>
+      </c>
       <c r="J895" s="2" t="n"/>
       <c r="K895" s="2" t="inlineStr"/>
       <c r="L895" s="2" t="inlineStr">
@@ -49310,7 +48836,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G896" t="inlineStr"/>
       <c r="H896" s="1" t="inlineStr"/>
       <c r="I896" s="2" t="n"/>
       <c r="J896" s="2" t="n"/>
@@ -49366,7 +48891,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G897" t="inlineStr"/>
       <c r="H897" s="1" t="n">
         <v>0</v>
       </c>
@@ -49422,7 +48946,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G898" t="inlineStr"/>
       <c r="H898" s="1" t="n">
         <v>0</v>
       </c>
@@ -49469,7 +48992,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G899" t="inlineStr"/>
       <c r="H899" s="1" t="inlineStr"/>
       <c r="I899" s="2" t="inlineStr">
         <is>
@@ -49514,7 +49036,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G900" t="inlineStr"/>
       <c r="H900" s="1" t="n">
         <v>0</v>
       </c>
@@ -49561,7 +49082,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G901" t="inlineStr"/>
       <c r="H901" s="1" t="inlineStr"/>
       <c r="I901" s="2" t="inlineStr">
         <is>
@@ -49618,7 +49138,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G902" t="inlineStr"/>
       <c r="H902" s="1" t="inlineStr"/>
       <c r="I902" s="2" t="inlineStr">
         <is>
@@ -49675,7 +49194,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G903" t="inlineStr"/>
       <c r="H903" s="1" t="n">
         <v>0</v>
       </c>
@@ -49736,7 +49254,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G905" t="inlineStr"/>
       <c r="H905" s="1" t="n">
         <v>0</v>
       </c>
@@ -49783,7 +49300,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G906" t="inlineStr"/>
       <c r="H906" s="1" t="inlineStr"/>
       <c r="I906" s="2" t="n"/>
       <c r="J906" s="2" t="n"/>
@@ -49894,7 +49410,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G908" t="inlineStr"/>
       <c r="H908" s="1" t="inlineStr"/>
       <c r="I908" s="2" t="inlineStr">
         <is>
@@ -49949,7 +49464,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G909" t="inlineStr"/>
       <c r="H909" s="1" t="n">
         <v>0</v>
       </c>
@@ -50044,7 +49558,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G915" t="inlineStr"/>
       <c r="H915" s="1" t="n">
         <v>0</v>
       </c>
@@ -50091,7 +49604,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G916" t="inlineStr"/>
       <c r="H916" s="1" t="n">
         <v>0</v>
       </c>
@@ -50147,7 +49659,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G917" t="inlineStr"/>
       <c r="H917" s="1" t="inlineStr"/>
       <c r="I917" s="2" t="inlineStr">
         <is>
@@ -50202,7 +49713,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G918" t="inlineStr"/>
       <c r="H918" s="1" t="n">
         <v>0</v>
       </c>
@@ -50309,7 +49819,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G920" t="inlineStr"/>
       <c r="H920" s="1" t="n">
         <v>0</v>
       </c>
@@ -50356,7 +49865,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G921" t="inlineStr"/>
       <c r="H921" s="1" t="inlineStr"/>
       <c r="I921" s="2" t="n"/>
       <c r="J921" s="2" t="n"/>
@@ -50412,7 +49920,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G922" t="inlineStr"/>
       <c r="H922" s="1" t="n">
         <v>0</v>
       </c>
@@ -50528,9 +50035,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G924" t="inlineStr"/>
       <c r="H924" s="1" t="inlineStr"/>
-      <c r="I924" s="2" t="n"/>
+      <c r="I924" s="2" t="inlineStr">
+        <is>
+          <t>847294009117</t>
+        </is>
+      </c>
       <c r="J924" s="2" t="n"/>
       <c r="K924" s="2" t="inlineStr"/>
       <c r="L924" s="2" t="inlineStr">
@@ -50584,7 +50094,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G925" t="inlineStr"/>
       <c r="H925" s="1" t="inlineStr"/>
       <c r="I925" s="2" t="inlineStr">
         <is>
@@ -50706,9 +50215,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G927" t="inlineStr"/>
       <c r="H927" s="1" t="inlineStr"/>
-      <c r="I927" s="2" t="n"/>
+      <c r="I927" s="2" t="inlineStr">
+        <is>
+          <t>847294002712</t>
+        </is>
+      </c>
       <c r="J927" s="2" t="n"/>
       <c r="K927" s="2" t="inlineStr"/>
       <c r="L927" s="2" t="inlineStr">
@@ -50822,7 +50334,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G929" t="inlineStr"/>
       <c r="H929" s="1" t="n">
         <v>0</v>
       </c>
@@ -50879,7 +50390,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G930" t="inlineStr"/>
       <c r="H930" s="1" t="inlineStr"/>
       <c r="I930" s="2" t="inlineStr">
         <is>
@@ -50929,9 +50439,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G931" t="inlineStr"/>
       <c r="H931" s="1" t="inlineStr"/>
-      <c r="I931" s="2" t="n"/>
+      <c r="I931" s="2" t="inlineStr">
+        <is>
+          <t>676821106629</t>
+        </is>
+      </c>
       <c r="J931" s="2" t="n"/>
       <c r="K931" s="2" t="inlineStr"/>
       <c r="L931" s="2" t="inlineStr">
@@ -50980,7 +50493,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G932" t="inlineStr"/>
       <c r="H932" s="1" t="inlineStr"/>
       <c r="I932" s="2" t="n"/>
       <c r="J932" s="2" t="n"/>
@@ -51091,7 +50603,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G934" t="inlineStr"/>
       <c r="H934" s="1" t="inlineStr"/>
       <c r="I934" s="2" t="inlineStr">
         <is>
@@ -51151,7 +50662,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G935" t="inlineStr"/>
       <c r="H935" s="1" t="inlineStr"/>
       <c r="I935" s="2" t="inlineStr">
         <is>
@@ -51205,9 +50715,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G936" t="inlineStr"/>
       <c r="H936" s="1" t="inlineStr"/>
-      <c r="I936" s="2" t="n"/>
+      <c r="I936" s="2" t="inlineStr">
+        <is>
+          <t>847294089256</t>
+        </is>
+      </c>
       <c r="J936" s="2" t="n"/>
       <c r="K936" s="2" t="inlineStr"/>
       <c r="L936" s="2" t="inlineStr">
@@ -51256,7 +50769,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G937" t="inlineStr"/>
       <c r="H937" s="1" t="inlineStr"/>
       <c r="I937" s="2" t="inlineStr">
         <is>
@@ -51311,7 +50823,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G938" t="inlineStr"/>
       <c r="H938" s="1" t="n">
         <v>0</v>
       </c>
@@ -51358,7 +50869,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G939" t="inlineStr"/>
       <c r="H939" s="1" t="inlineStr"/>
       <c r="I939" s="2" t="inlineStr">
         <is>
@@ -51413,7 +50923,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G940" t="inlineStr"/>
       <c r="H940" s="1" t="n">
         <v>0</v>
       </c>
@@ -51469,7 +50978,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G941" t="inlineStr"/>
       <c r="H941" s="1" t="inlineStr"/>
       <c r="I941" s="2" t="n"/>
       <c r="J941" s="2" t="n"/>
@@ -51582,7 +51090,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G943" t="inlineStr"/>
       <c r="H943" s="1" t="n">
         <v>0</v>
       </c>
@@ -51638,7 +51145,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G944" t="inlineStr"/>
       <c r="H944" s="1" t="n">
         <v>0</v>
       </c>
@@ -51695,7 +51201,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G945" t="inlineStr"/>
       <c r="H945" s="1" t="n">
         <v>0</v>
       </c>
@@ -51752,7 +51257,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G946" t="inlineStr"/>
       <c r="H946" s="1" t="n">
         <v>0</v>
       </c>
@@ -51808,7 +51312,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G947" t="inlineStr"/>
       <c r="H947" s="1" t="n">
         <v>0</v>
       </c>
@@ -51855,7 +51358,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G948" t="inlineStr"/>
       <c r="H948" s="1" t="inlineStr"/>
       <c r="I948" s="2" t="n"/>
       <c r="J948" s="2" t="n"/>
@@ -51911,7 +51413,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G949" t="inlineStr"/>
       <c r="H949" s="1" t="n">
         <v>0</v>
       </c>
@@ -51967,7 +51468,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G950" t="inlineStr"/>
       <c r="H950" s="1" t="n">
         <v>0</v>
       </c>
@@ -52172,7 +51672,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G954" t="inlineStr"/>
       <c r="H954" s="1" t="n">
         <v>0</v>
       </c>
@@ -52224,7 +51723,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G955" t="inlineStr"/>
       <c r="H955" s="1" t="inlineStr"/>
       <c r="I955" s="2" t="n"/>
       <c r="J955" s="2" t="n"/>
@@ -52280,7 +51778,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G956" t="inlineStr"/>
       <c r="H956" s="1" t="n">
         <v>0</v>
       </c>
@@ -52336,7 +51833,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G957" t="inlineStr"/>
       <c r="H957" s="1" t="n">
         <v>0</v>
       </c>
@@ -52390,7 +51886,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G958" t="inlineStr"/>
       <c r="H958" s="1" t="inlineStr"/>
       <c r="I958" s="2" t="inlineStr">
         <is>
@@ -52445,7 +51940,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G959" t="inlineStr"/>
       <c r="H959" s="1" t="n">
         <v>0</v>
       </c>
@@ -52531,7 +52025,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G963" t="inlineStr"/>
       <c r="H963" s="1" t="n">
         <v>0</v>
       </c>
@@ -52578,7 +52071,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G964" t="inlineStr"/>
       <c r="H964" s="1" t="inlineStr"/>
       <c r="I964" s="2" t="inlineStr">
         <is>
@@ -52623,7 +52115,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G965" t="inlineStr"/>
       <c r="H965" s="1" t="n">
         <v>0</v>
       </c>
@@ -52679,7 +52170,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G966" t="inlineStr"/>
       <c r="H966" s="1" t="n">
         <v>0</v>
       </c>
@@ -52726,7 +52216,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G967" t="inlineStr"/>
       <c r="H967" s="1" t="inlineStr"/>
       <c r="I967" s="2" t="n"/>
       <c r="J967" s="2" t="n"/>
@@ -52787,7 +52276,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G969" t="inlineStr"/>
       <c r="H969" s="1" t="n">
         <v>0</v>
       </c>
@@ -52839,7 +52327,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G970" t="inlineStr"/>
       <c r="H970" s="1" t="n">
         <v>0</v>
       </c>
@@ -52895,7 +52382,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G971" t="inlineStr"/>
       <c r="H971" s="1" t="n">
         <v>0</v>
       </c>
@@ -52947,7 +52433,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G972" t="inlineStr"/>
       <c r="H972" s="1" t="n">
         <v>0</v>
       </c>
@@ -53003,7 +52488,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G973" t="inlineStr"/>
       <c r="H973" s="1" t="n">
         <v>0</v>
       </c>
@@ -53110,7 +52594,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G975" t="inlineStr"/>
       <c r="H975" s="1" t="n">
         <v>0</v>
       </c>
@@ -53167,7 +52650,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G976" t="inlineStr"/>
       <c r="H976" s="1" t="inlineStr"/>
       <c r="I976" s="2" t="inlineStr">
         <is>
@@ -53222,7 +52704,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G977" t="inlineStr"/>
       <c r="H977" s="1" t="n">
         <v>0</v>
       </c>
@@ -53269,7 +52750,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G978" t="inlineStr"/>
       <c r="H978" s="1" t="n">
         <v>0</v>
       </c>
@@ -53316,7 +52796,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G979" t="inlineStr"/>
       <c r="H979" s="1" t="n">
         <v>0</v>
       </c>
@@ -53367,7 +52846,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G980" t="inlineStr"/>
       <c r="H980" s="1" t="n">
         <v>0</v>
       </c>
@@ -53423,7 +52901,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G981" t="inlineStr"/>
       <c r="H981" s="1" t="n">
         <v>0</v>
       </c>
@@ -53470,7 +52947,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G982" t="inlineStr"/>
       <c r="H982" s="1" t="n">
         <v>0</v>
       </c>
@@ -53517,7 +52993,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G983" t="inlineStr"/>
       <c r="H983" s="1" t="inlineStr"/>
       <c r="I983" s="2" t="inlineStr">
         <is>
@@ -53577,7 +53052,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G984" t="inlineStr"/>
       <c r="H984" s="1" t="n">
         <v>0</v>
       </c>
@@ -53624,7 +53098,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G985" t="inlineStr"/>
       <c r="H985" s="1" t="inlineStr"/>
       <c r="I985" s="2" t="inlineStr">
         <is>
@@ -53679,7 +53152,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G986" t="inlineStr"/>
       <c r="H986" s="1" t="n">
         <v>0</v>
       </c>
@@ -53786,7 +53258,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G988" t="inlineStr"/>
       <c r="H988" s="1" t="inlineStr"/>
       <c r="I988" s="2" t="n"/>
       <c r="J988" s="2" t="n"/>
@@ -53837,7 +53308,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G989" t="inlineStr"/>
       <c r="H989" s="1" t="n">
         <v>0</v>
       </c>
@@ -53893,7 +53363,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G990" t="inlineStr"/>
       <c r="H990" s="1" t="n">
         <v>0</v>
       </c>
@@ -53945,7 +53414,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G991" t="inlineStr"/>
       <c r="H991" s="1" t="n">
         <v>0</v>
       </c>
@@ -54061,7 +53529,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G993" t="inlineStr"/>
       <c r="H993" s="1" t="inlineStr"/>
       <c r="I993" s="2" t="inlineStr">
         <is>
@@ -54181,7 +53648,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G995" t="inlineStr"/>
       <c r="H995" s="1" t="n">
         <v>0</v>
       </c>
@@ -54308,7 +53774,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G998" t="inlineStr"/>
       <c r="H998" s="1" t="n">
         <v>0</v>
       </c>
@@ -54355,7 +53820,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G999" t="inlineStr"/>
       <c r="H999" s="1" t="inlineStr"/>
       <c r="I999" s="2" t="inlineStr">
         <is>
@@ -54466,7 +53930,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1001" t="inlineStr"/>
       <c r="H1001" s="1" t="inlineStr"/>
       <c r="I1001" s="2" t="n"/>
       <c r="J1001" s="2" t="n"/>
@@ -54524,7 +53987,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1002" t="inlineStr"/>
       <c r="H1002" s="1" t="inlineStr"/>
       <c r="I1002" s="2" t="inlineStr">
         <is>
@@ -54579,7 +54041,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1003" t="inlineStr"/>
       <c r="H1003" s="1" t="inlineStr"/>
       <c r="I1003" s="2" t="inlineStr">
         <is>
@@ -54624,7 +54085,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1004" t="inlineStr"/>
       <c r="H1004" s="1" t="inlineStr"/>
       <c r="I1004" s="2" t="n"/>
       <c r="J1004" s="2" t="n"/>
@@ -54675,7 +54135,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1005" t="inlineStr"/>
       <c r="H1005" s="1" t="inlineStr"/>
       <c r="I1005" s="2" t="n"/>
       <c r="J1005" s="2" t="n"/>
@@ -54731,7 +54190,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1006" t="inlineStr"/>
       <c r="H1006" s="1" t="n">
         <v>0</v>
       </c>
@@ -54787,7 +54245,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1007" t="inlineStr"/>
       <c r="H1007" s="1" t="inlineStr"/>
       <c r="I1007" s="2" t="inlineStr">
         <is>
@@ -54842,7 +54299,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1008" t="inlineStr"/>
       <c r="H1008" s="1" t="inlineStr"/>
       <c r="I1008" s="2" t="inlineStr">
         <is>
@@ -54887,7 +54343,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1009" t="inlineStr"/>
       <c r="H1009" s="1" t="n">
         <v>0</v>
       </c>
@@ -54943,7 +54398,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1010" t="inlineStr"/>
       <c r="H1010" s="1" t="n">
         <v>0</v>
       </c>
@@ -54999,7 +54453,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1011" t="inlineStr"/>
       <c r="H1011" s="1" t="inlineStr"/>
       <c r="I1011" s="2" t="inlineStr">
         <is>
@@ -55049,7 +54502,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1012" t="inlineStr"/>
       <c r="H1012" s="1" t="n">
         <v>0</v>
       </c>
@@ -55152,7 +54604,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1014" t="inlineStr"/>
       <c r="H1014" s="1" t="n">
         <v>0</v>
       </c>
@@ -55199,7 +54650,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1015" t="inlineStr"/>
       <c r="H1015" s="1" t="inlineStr"/>
       <c r="I1015" s="2" t="n"/>
       <c r="J1015" s="2" t="n"/>
@@ -55255,7 +54705,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1016" t="inlineStr"/>
       <c r="H1016" s="1" t="n">
         <v>0</v>
       </c>
@@ -55307,7 +54756,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1017" t="inlineStr"/>
       <c r="H1017" s="1" t="n">
         <v>0</v>
       </c>
@@ -55359,7 +54807,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1018" t="inlineStr"/>
       <c r="H1018" s="1" t="n">
         <v>0</v>
       </c>
@@ -55411,7 +54858,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1019" t="inlineStr"/>
       <c r="H1019" s="1" t="n">
         <v>0</v>
       </c>
@@ -55538,7 +54984,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1022" t="inlineStr"/>
       <c r="H1022" s="1" t="n">
         <v>0</v>
       </c>
@@ -55594,7 +55039,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1023" t="inlineStr"/>
       <c r="H1023" s="1" t="inlineStr"/>
       <c r="I1023" s="2" t="inlineStr">
         <is>
@@ -55649,7 +55093,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1024" t="inlineStr"/>
       <c r="H1024" s="1" t="n">
         <v>0</v>
       </c>
@@ -55705,7 +55148,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1025" t="inlineStr"/>
       <c r="H1025" s="1" t="n">
         <v>0</v>
       </c>
@@ -55766,9 +55208,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1026" t="inlineStr"/>
       <c r="H1026" s="1" t="inlineStr"/>
-      <c r="I1026" s="2" t="n"/>
+      <c r="I1026" s="2" t="inlineStr">
+        <is>
+          <t>847294092423</t>
+        </is>
+      </c>
       <c r="J1026" s="2" t="n"/>
       <c r="K1026" s="2" t="inlineStr"/>
       <c r="L1026" s="2" t="inlineStr">
@@ -55817,7 +55262,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1027" t="inlineStr"/>
       <c r="H1027" s="1" t="inlineStr"/>
       <c r="I1027" s="2" t="inlineStr">
         <is>
@@ -55867,7 +55311,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1028" t="inlineStr"/>
       <c r="H1028" s="1" t="n">
         <v>0</v>
       </c>
@@ -55919,7 +55362,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1029" t="inlineStr"/>
       <c r="H1029" s="1" t="n">
         <v>0</v>
       </c>
@@ -55966,7 +55408,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1030" t="inlineStr"/>
       <c r="H1030" s="1" t="inlineStr"/>
       <c r="I1030" s="2" t="n"/>
       <c r="J1030" s="2" t="n"/>
@@ -56022,7 +55463,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1031" t="inlineStr"/>
       <c r="H1031" s="1" t="inlineStr"/>
       <c r="I1031" s="2" t="n"/>
       <c r="J1031" s="2" t="n"/>
@@ -56078,7 +55518,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1032" t="inlineStr"/>
       <c r="H1032" s="1" t="inlineStr"/>
       <c r="I1032" s="2" t="n"/>
       <c r="J1032" s="2" t="n"/>
@@ -56185,7 +55624,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1034" t="inlineStr"/>
       <c r="H1034" s="1" t="inlineStr"/>
       <c r="I1034" s="2" t="n"/>
       <c r="J1034" s="2" t="n"/>
@@ -56292,7 +55730,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1036" t="inlineStr"/>
       <c r="H1036" s="1" t="inlineStr"/>
       <c r="I1036" s="2" t="n"/>
       <c r="J1036" s="2" t="n"/>
@@ -56348,7 +55785,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1037" t="inlineStr"/>
       <c r="H1037" s="1" t="inlineStr"/>
       <c r="I1037" s="2" t="n"/>
       <c r="J1037" s="2" t="n"/>
@@ -56455,7 +55891,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1039" t="inlineStr"/>
       <c r="H1039" s="1" t="inlineStr"/>
       <c r="I1039" s="2" t="n"/>
       <c r="J1039" s="2" t="n"/>
@@ -56562,7 +55997,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1041" t="inlineStr"/>
       <c r="H1041" s="1" t="inlineStr"/>
       <c r="I1041" s="2" t="n"/>
       <c r="J1041" s="2" t="n"/>
@@ -56618,7 +56052,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1042" t="inlineStr"/>
       <c r="H1042" s="1" t="n">
         <v>0</v>
       </c>
@@ -56675,7 +56108,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1043" t="inlineStr"/>
       <c r="H1043" s="1" t="n">
         <v>0</v>
       </c>
@@ -56727,7 +56159,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1044" t="inlineStr"/>
       <c r="H1044" s="1" t="inlineStr"/>
       <c r="I1044" s="2" t="n"/>
       <c r="J1044" s="2" t="n"/>
@@ -56778,7 +56209,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1045" t="inlineStr"/>
       <c r="H1045" s="1" t="n">
         <v>0</v>
       </c>
@@ -56834,7 +56264,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1046" t="inlineStr"/>
       <c r="H1046" s="1" t="n">
         <v>0</v>
       </c>
@@ -57071,9 +56500,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1050" t="inlineStr"/>
       <c r="H1050" s="1" t="inlineStr"/>
-      <c r="I1050" s="2" t="n"/>
+      <c r="I1050" s="2" t="inlineStr">
+        <is>
+          <t>6950165403014</t>
+        </is>
+      </c>
       <c r="J1050" s="2" t="n"/>
       <c r="K1050" s="2" t="inlineStr"/>
       <c r="L1050" s="2" t="inlineStr">
@@ -57127,7 +56559,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1051" t="inlineStr"/>
       <c r="H1051" s="1" t="n">
         <v>0</v>
       </c>
@@ -57174,7 +56605,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1052" t="inlineStr"/>
       <c r="H1052" s="1" t="inlineStr"/>
       <c r="I1052" s="2" t="inlineStr">
         <is>
@@ -57229,7 +56659,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1053" t="inlineStr"/>
       <c r="H1053" s="1" t="n">
         <v>0</v>
       </c>
@@ -57342,7 +56771,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1055" t="inlineStr"/>
       <c r="H1055" s="1" t="inlineStr"/>
       <c r="I1055" s="2" t="n"/>
       <c r="J1055" s="2" t="n"/>
@@ -57398,7 +56826,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1056" t="inlineStr"/>
       <c r="H1056" s="1" t="inlineStr"/>
       <c r="I1056" s="2" t="n"/>
       <c r="J1056" s="2" t="n"/>
@@ -57564,7 +56991,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1059" t="inlineStr"/>
       <c r="H1059" s="1" t="inlineStr"/>
       <c r="I1059" s="2" t="inlineStr">
         <is>
@@ -57629,7 +57055,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1061" t="inlineStr"/>
       <c r="H1061" s="1" t="n">
         <v>0</v>
       </c>
@@ -57740,7 +57165,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1063" t="inlineStr"/>
       <c r="H1063" s="1" t="n">
         <v>0</v>
       </c>
@@ -57787,7 +57211,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1064" t="inlineStr"/>
       <c r="H1064" s="1" t="inlineStr"/>
       <c r="I1064" s="2" t="inlineStr">
         <is>
@@ -57842,7 +57265,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1065" t="inlineStr"/>
       <c r="H1065" s="1" t="n">
         <v>0</v>
       </c>
@@ -57898,7 +57320,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1066" t="inlineStr"/>
       <c r="H1066" s="1" t="n">
         <v>0</v>
       </c>
@@ -57954,7 +57375,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1067" t="inlineStr"/>
       <c r="H1067" s="1" t="inlineStr"/>
       <c r="I1067" s="2" t="n"/>
       <c r="J1067" s="2" t="n"/>
@@ -58015,7 +57435,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1069" t="inlineStr"/>
       <c r="H1069" s="1" t="n">
         <v>0</v>
       </c>
@@ -58071,7 +57490,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1070" t="inlineStr"/>
       <c r="H1070" s="1" t="inlineStr"/>
       <c r="I1070" s="2" t="inlineStr">
         <is>
@@ -58191,7 +57609,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1072" t="inlineStr"/>
       <c r="H1072" s="1" t="inlineStr"/>
       <c r="I1072" s="2" t="n"/>
       <c r="J1072" s="2" t="n"/>
@@ -58242,7 +57659,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1073" t="inlineStr"/>
       <c r="H1073" s="1" t="n">
         <v>0</v>
       </c>
@@ -58298,7 +57714,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1074" t="inlineStr"/>
       <c r="H1074" s="1" t="n">
         <v>0</v>
       </c>
@@ -58350,7 +57765,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1075" t="inlineStr"/>
       <c r="H1075" s="1" t="n">
         <v>0</v>
       </c>
@@ -58402,9 +57816,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1076" t="inlineStr"/>
       <c r="H1076" s="1" t="inlineStr"/>
-      <c r="I1076" s="2" t="n"/>
+      <c r="I1076" s="2" t="inlineStr">
+        <is>
+          <t>676821466891</t>
+        </is>
+      </c>
       <c r="J1076" s="2" t="n"/>
       <c r="K1076" s="2" t="inlineStr"/>
       <c r="L1076" s="2" t="inlineStr">
@@ -58453,7 +57870,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1077" t="inlineStr"/>
       <c r="H1077" s="1" t="n">
         <v>0</v>
       </c>
@@ -58500,7 +57916,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1078" t="inlineStr"/>
       <c r="H1078" s="1" t="inlineStr"/>
       <c r="I1078" s="2" t="inlineStr">
         <is>
@@ -58555,7 +57970,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1079" t="inlineStr"/>
       <c r="H1079" s="1" t="n">
         <v>0</v>
       </c>
@@ -58607,11 +58021,14 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1080" t="inlineStr"/>
       <c r="H1080" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I1080" s="2" t="n"/>
+      <c r="I1080" s="2" t="inlineStr">
+        <is>
+          <t>676821261632</t>
+        </is>
+      </c>
       <c r="J1080" s="2" t="n"/>
       <c r="K1080" s="2" t="inlineStr"/>
       <c r="L1080" s="2" t="inlineStr">
@@ -58655,9 +58072,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1081" t="inlineStr"/>
       <c r="H1081" s="1" t="inlineStr"/>
-      <c r="I1081" s="2" t="n"/>
+      <c r="I1081" s="2" t="inlineStr">
+        <is>
+          <t>676821261632</t>
+        </is>
+      </c>
       <c r="J1081" s="2" t="n"/>
       <c r="K1081" s="2" t="inlineStr"/>
       <c r="L1081" s="2" t="inlineStr">
@@ -58706,7 +58126,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1082" t="inlineStr"/>
       <c r="H1082" s="1" t="inlineStr"/>
       <c r="I1082" s="2" t="n"/>
       <c r="J1082" s="2" t="n"/>
@@ -58797,7 +58216,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1087" t="inlineStr"/>
       <c r="H1087" s="1" t="n">
         <v>0</v>
       </c>
@@ -58853,7 +58271,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1088" t="inlineStr"/>
       <c r="H1088" s="1" t="n">
         <v>0</v>
       </c>
@@ -58956,7 +58373,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1090" t="inlineStr"/>
       <c r="H1090" s="1" t="inlineStr"/>
       <c r="I1090" s="2" t="inlineStr">
         <is>
@@ -59069,9 +58485,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1092" t="inlineStr"/>
       <c r="H1092" s="1" t="inlineStr"/>
-      <c r="I1092" s="2" t="n"/>
+      <c r="I1092" s="2" t="inlineStr">
+        <is>
+          <t>847294017150</t>
+        </is>
+      </c>
       <c r="J1092" s="2" t="n"/>
       <c r="K1092" s="2" t="inlineStr"/>
       <c r="L1092" s="2" t="inlineStr">
@@ -59125,7 +58544,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1093" t="inlineStr"/>
       <c r="H1093" s="1" t="n">
         <v>0</v>
       </c>
@@ -59181,7 +58599,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1094" t="inlineStr"/>
       <c r="H1094" s="1" t="n">
         <v>0</v>
       </c>
@@ -59238,7 +58655,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1095" t="inlineStr"/>
       <c r="H1095" s="1" t="n">
         <v>0</v>
       </c>
@@ -59294,7 +58710,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1096" t="inlineStr"/>
       <c r="H1096" s="1" t="n">
         <v>0</v>
       </c>
@@ -59350,7 +58765,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1097" t="inlineStr"/>
       <c r="H1097" s="1" t="n">
         <v>0</v>
       </c>
@@ -59399,7 +58813,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1098" t="inlineStr"/>
       <c r="H1098" s="1" t="inlineStr"/>
       <c r="I1098" s="2" t="inlineStr">
         <is>
@@ -59461,7 +58874,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1099" t="inlineStr"/>
       <c r="H1099" s="1" t="n">
         <v>0</v>
       </c>
@@ -59517,9 +58929,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1100" t="inlineStr"/>
       <c r="H1100" s="1" t="inlineStr"/>
-      <c r="I1100" s="2" t="n"/>
+      <c r="I1100" s="2" t="inlineStr">
+        <is>
+          <t>676821384287</t>
+        </is>
+      </c>
       <c r="J1100" s="2" t="n"/>
       <c r="K1100" s="2" t="inlineStr"/>
       <c r="L1100" s="2" t="inlineStr">
@@ -59568,7 +58983,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1101" t="inlineStr"/>
       <c r="H1101" s="1" t="n">
         <v>0</v>
       </c>
@@ -59615,7 +59029,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1102" t="inlineStr"/>
       <c r="H1102" s="1" t="inlineStr"/>
       <c r="I1102" s="2" t="n"/>
       <c r="J1102" s="2" t="n"/>
@@ -59726,7 +59139,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1104" t="inlineStr"/>
       <c r="H1104" s="1" t="n">
         <v>0</v>
       </c>
@@ -59778,7 +59190,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1105" t="inlineStr"/>
       <c r="H1105" s="1" t="inlineStr"/>
       <c r="I1105" s="2" t="n"/>
       <c r="J1105" s="2" t="n"/>
@@ -59829,7 +59240,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1106" t="inlineStr"/>
       <c r="H1106" s="1" t="n">
         <v>0</v>
       </c>
@@ -59885,7 +59295,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1107" t="inlineStr"/>
       <c r="H1107" s="1" t="n">
         <v>0</v>
       </c>
@@ -60000,9 +59409,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1109" t="inlineStr"/>
       <c r="H1109" s="1" t="inlineStr"/>
-      <c r="I1109" s="2" t="n"/>
+      <c r="I1109" s="2" t="inlineStr">
+        <is>
+          <t>805253500068</t>
+        </is>
+      </c>
       <c r="J1109" s="2" t="n"/>
       <c r="K1109" s="2" t="inlineStr"/>
       <c r="L1109" s="2" t="inlineStr">
@@ -60113,7 +59525,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1111" t="inlineStr"/>
       <c r="H1111" s="1" t="n">
         <v>0</v>
       </c>
@@ -60235,7 +59646,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1114" t="inlineStr"/>
       <c r="H1114" s="1" t="n">
         <v>0</v>
       </c>
@@ -60282,7 +59692,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1115" t="inlineStr"/>
       <c r="H1115" s="1" t="inlineStr"/>
       <c r="I1115" s="2" t="n"/>
       <c r="J1115" s="2" t="n"/>
@@ -60394,7 +59803,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1117" t="inlineStr"/>
       <c r="H1117" s="1" t="n">
         <v>0</v>
       </c>
@@ -60613,7 +60021,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1121" t="inlineStr"/>
       <c r="H1121" s="1" t="inlineStr"/>
       <c r="I1121" s="2" t="n"/>
       <c r="J1121" s="2" t="n"/>
@@ -60669,7 +60076,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1122" t="inlineStr"/>
       <c r="H1122" s="1" t="n">
         <v>0</v>
       </c>
@@ -60721,7 +60127,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1123" t="inlineStr"/>
       <c r="H1123" s="1" t="n">
         <v>0</v>
       </c>
@@ -60768,7 +60173,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1124" t="inlineStr"/>
       <c r="H1124" s="1" t="inlineStr"/>
       <c r="I1124" s="2" t="n"/>
       <c r="J1124" s="2" t="n"/>
@@ -60819,7 +60223,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1125" t="inlineStr"/>
       <c r="H1125" s="1" t="inlineStr"/>
       <c r="I1125" s="2" t="n"/>
       <c r="J1125" s="2" t="n"/>
@@ -60870,7 +60273,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1126" t="inlineStr"/>
       <c r="H1126" s="1" t="n">
         <v>0</v>
       </c>
@@ -60919,7 +60321,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1127" t="inlineStr"/>
       <c r="H1127" s="1" t="inlineStr"/>
       <c r="I1127" s="2" t="n"/>
       <c r="J1127" s="2" t="n"/>
@@ -60975,7 +60376,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1128" t="inlineStr"/>
       <c r="H1128" s="1" t="n">
         <v>0</v>
       </c>
@@ -61026,7 +60426,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1129" t="inlineStr"/>
       <c r="H1129" s="1" t="inlineStr"/>
       <c r="I1129" s="2" t="inlineStr">
         <is>
@@ -61137,7 +60536,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1131" t="inlineStr"/>
       <c r="H1131" s="1" t="inlineStr"/>
       <c r="I1131" s="2" t="n"/>
       <c r="J1131" s="2" t="n"/>
@@ -61244,7 +60642,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1133" t="inlineStr"/>
       <c r="H1133" s="1" t="inlineStr"/>
       <c r="I1133" s="2" t="n"/>
       <c r="J1133" s="2" t="n"/>
@@ -61361,7 +60758,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1135" t="inlineStr"/>
       <c r="H1135" s="1" t="inlineStr"/>
       <c r="I1135" s="2" t="n"/>
       <c r="J1135" s="2" t="n"/>
@@ -61649,7 +61045,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1140" t="inlineStr"/>
       <c r="H1140" s="1" t="inlineStr"/>
       <c r="I1140" s="2" t="n"/>
       <c r="J1140" s="2" t="n"/>
@@ -61816,7 +61211,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1143" t="inlineStr"/>
       <c r="H1143" s="1" t="n">
         <v>0</v>
       </c>
@@ -61873,7 +61267,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1144" t="inlineStr"/>
       <c r="H1144" s="1" t="n">
         <v>0</v>
       </c>
@@ -61930,7 +61323,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1145" t="inlineStr"/>
       <c r="H1145" s="1" t="n">
         <v>0</v>
       </c>
@@ -62037,7 +61429,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1147" t="inlineStr"/>
       <c r="H1147" s="1" t="n">
         <v>0</v>
       </c>
@@ -62094,7 +61485,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1148" t="inlineStr"/>
       <c r="H1148" s="1" t="inlineStr"/>
       <c r="I1148" s="2" t="n"/>
       <c r="J1148" s="2" t="n"/>
@@ -62145,9 +61535,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1149" t="inlineStr"/>
       <c r="H1149" s="1" t="inlineStr"/>
-      <c r="I1149" s="2" t="n"/>
+      <c r="I1149" s="2" t="inlineStr">
+        <is>
+          <t>601527923911</t>
+        </is>
+      </c>
       <c r="J1149" s="2" t="n"/>
       <c r="K1149" s="2" t="inlineStr"/>
       <c r="L1149" s="2" t="inlineStr">
@@ -62196,7 +61589,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1150" t="inlineStr"/>
       <c r="H1150" s="1" t="n">
         <v>0</v>
       </c>
@@ -62322,7 +61714,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1153" t="inlineStr"/>
       <c r="H1153" s="1" t="n">
         <v>0</v>
       </c>
@@ -62374,7 +61765,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1154" t="inlineStr"/>
       <c r="H1154" s="1" t="inlineStr"/>
       <c r="I1154" s="2" t="n"/>
       <c r="J1154" s="2" t="n"/>
@@ -62425,7 +61815,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1155" t="inlineStr"/>
       <c r="H1155" s="1" t="n">
         <v>0</v>
       </c>
@@ -62477,7 +61866,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1156" t="inlineStr"/>
       <c r="H1156" s="1" t="n">
         <v>0</v>
       </c>
@@ -62529,7 +61917,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1157" t="inlineStr"/>
       <c r="H1157" s="1" t="n">
         <v>0</v>
       </c>
@@ -62576,7 +61963,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1158" t="inlineStr"/>
       <c r="H1158" s="1" t="n">
         <v>0</v>
       </c>
@@ -62632,7 +62018,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1159" t="inlineStr"/>
       <c r="H1159" s="1" t="n">
         <v>0</v>
       </c>
@@ -62688,7 +62073,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1160" t="inlineStr"/>
       <c r="H1160" s="1" t="n">
         <v>0</v>
       </c>
@@ -62744,7 +62128,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1161" t="inlineStr"/>
       <c r="H1161" s="1" t="n">
         <v>0</v>
       </c>
@@ -62801,7 +62184,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1162" t="inlineStr"/>
       <c r="H1162" s="1" t="n">
         <v>0</v>
       </c>
@@ -62854,7 +62236,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1163" t="inlineStr"/>
       <c r="H1163" s="1" t="n">
         <v>0</v>
       </c>
@@ -62901,7 +62282,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1164" t="inlineStr"/>
       <c r="H1164" s="1" t="inlineStr"/>
       <c r="I1164" s="2" t="inlineStr">
         <is>
@@ -62951,7 +62331,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1165" t="inlineStr"/>
       <c r="H1165" s="1" t="inlineStr"/>
       <c r="I1165" s="2" t="inlineStr">
         <is>
@@ -63061,7 +62440,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1167" t="inlineStr"/>
       <c r="H1167" s="1" t="inlineStr"/>
       <c r="I1167" s="2" t="inlineStr">
         <is>
@@ -63121,7 +62499,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1168" t="inlineStr"/>
       <c r="H1168" s="1" t="n">
         <v>0</v>
       </c>
@@ -63177,7 +62554,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1169" t="inlineStr"/>
       <c r="H1169" s="1" t="inlineStr"/>
       <c r="I1169" s="45" t="n">
         <v>757205302971</v>
@@ -63235,7 +62611,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1170" t="inlineStr"/>
       <c r="H1170" s="1" t="n">
         <v>0</v>
       </c>
@@ -63302,7 +62677,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1172" t="inlineStr"/>
       <c r="H1172" s="1" t="n">
         <v>0</v>
       </c>
@@ -63409,7 +62783,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1174" t="inlineStr"/>
       <c r="H1174" s="1" t="inlineStr"/>
       <c r="I1174" s="2" t="n"/>
       <c r="J1174" s="2" t="n"/>
@@ -63465,9 +62838,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1175" t="inlineStr"/>
       <c r="H1175" s="1" t="inlineStr"/>
-      <c r="I1175" s="2" t="n"/>
+      <c r="I1175" s="2" t="inlineStr">
+        <is>
+          <t>676821352187</t>
+        </is>
+      </c>
       <c r="J1175" s="2" t="n"/>
       <c r="K1175" s="2" t="inlineStr"/>
       <c r="L1175" s="2" t="inlineStr">
@@ -63516,7 +62892,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1176" t="inlineStr"/>
       <c r="H1176" s="1" t="inlineStr"/>
       <c r="I1176" s="45" t="n">
         <v>753459865088</v>
@@ -63564,7 +62939,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1177" t="inlineStr"/>
       <c r="H1177" s="1" t="inlineStr"/>
       <c r="I1177" s="2" t="inlineStr">
         <is>
@@ -63626,7 +63000,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1178" t="inlineStr"/>
       <c r="H1178" s="1" t="inlineStr"/>
       <c r="I1178" s="2" t="inlineStr">
         <is>
@@ -63686,7 +63059,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1179" t="inlineStr"/>
       <c r="H1179" s="1" t="inlineStr"/>
       <c r="I1179" s="2" t="inlineStr">
         <is>
@@ -63736,7 +63108,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1180" t="inlineStr"/>
       <c r="H1180" s="1" t="n">
         <v>0</v>
       </c>
@@ -63792,7 +63163,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1181" t="inlineStr"/>
       <c r="H1181" s="1" t="inlineStr"/>
       <c r="I1181" s="2" t="inlineStr">
         <is>
@@ -63847,7 +63217,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1182" t="inlineStr"/>
       <c r="H1182" s="1" t="n">
         <v>0</v>
       </c>
@@ -63894,7 +63263,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1183" t="inlineStr"/>
       <c r="H1183" s="1" t="n">
         <v>0</v>
       </c>
@@ -63942,7 +63310,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1184" t="inlineStr"/>
       <c r="H1184" s="1" t="n">
         <v>0</v>
       </c>
@@ -63990,7 +63357,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1185" t="inlineStr"/>
       <c r="H1185" s="1" t="n">
         <v>0</v>
       </c>
@@ -64042,7 +63408,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1186" t="inlineStr"/>
       <c r="H1186" s="1" t="n">
         <v>0</v>
       </c>
@@ -64094,7 +63459,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1187" t="inlineStr"/>
       <c r="H1187" s="1" t="n">
         <v>0</v>
       </c>
@@ -64146,7 +63510,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1188" t="inlineStr"/>
       <c r="H1188" s="1" t="n">
         <v>0</v>
       </c>
@@ -64198,7 +63561,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1189" t="inlineStr"/>
       <c r="H1189" s="1" t="inlineStr"/>
       <c r="I1189" s="2" t="inlineStr">
         <is>
@@ -64318,7 +63680,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1191" t="inlineStr"/>
       <c r="H1191" s="1" t="inlineStr"/>
       <c r="I1191" s="2" t="inlineStr">
         <is>
@@ -64378,7 +63739,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1192" t="inlineStr"/>
       <c r="H1192" s="1" t="inlineStr"/>
       <c r="I1192" s="2" t="inlineStr">
         <is>
@@ -64430,7 +63790,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1193" t="inlineStr"/>
       <c r="H1193" s="1" t="inlineStr"/>
       <c r="I1193" s="2" t="inlineStr">
         <is>
@@ -64485,7 +63844,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1194" t="inlineStr"/>
       <c r="H1194" s="1" t="inlineStr"/>
       <c r="I1194" s="2" t="inlineStr">
         <is>
@@ -64537,7 +63895,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1195" t="inlineStr"/>
       <c r="H1195" s="1" t="inlineStr"/>
       <c r="I1195" s="2" t="inlineStr">
         <is>
@@ -64594,7 +63951,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1196" t="inlineStr"/>
       <c r="H1196" s="1" t="inlineStr"/>
       <c r="I1196" s="2" t="inlineStr">
         <is>
@@ -64646,7 +64002,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1197" t="inlineStr"/>
       <c r="H1197" s="1" t="inlineStr"/>
       <c r="I1197" s="2" t="inlineStr">
         <is>
@@ -64691,7 +64046,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1198" t="inlineStr"/>
       <c r="H1198" s="1" t="n">
         <v>0</v>
       </c>
@@ -64734,7 +64088,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1199" t="inlineStr"/>
       <c r="H1199" s="1" t="n">
         <v>0</v>
       </c>
@@ -64850,7 +64203,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1201" t="inlineStr"/>
       <c r="H1201" s="1" t="inlineStr"/>
       <c r="I1201" s="2" t="n"/>
       <c r="J1201" s="2" t="n"/>
@@ -64901,7 +64253,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1202" t="inlineStr"/>
       <c r="H1202" s="1" t="n">
         <v>0</v>
       </c>
@@ -64957,7 +64308,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1203" t="inlineStr"/>
       <c r="H1203" s="1" t="n">
         <v>0</v>
       </c>
@@ -65013,7 +64363,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1204" t="inlineStr"/>
       <c r="H1204" s="1" t="n">
         <v>0</v>
       </c>
@@ -65069,7 +64418,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1205" t="inlineStr"/>
       <c r="H1205" s="1" t="n">
         <v>0</v>
       </c>
@@ -65116,7 +64464,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1206" t="inlineStr"/>
       <c r="H1206" s="1" t="inlineStr"/>
       <c r="I1206" s="2" t="inlineStr">
         <is>
@@ -65282,7 +64629,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1209" t="inlineStr"/>
       <c r="H1209" s="1" t="n">
         <v>0</v>
       </c>
@@ -65338,7 +64684,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1210" t="inlineStr"/>
       <c r="H1210" s="1" t="n">
         <v>0</v>
       </c>
@@ -65394,7 +64739,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1211" t="inlineStr"/>
       <c r="H1211" s="1" t="n">
         <v>0</v>
       </c>
@@ -65441,7 +64785,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1212" t="inlineStr"/>
       <c r="H1212" s="1" t="n">
         <v>0</v>
       </c>
@@ -65497,7 +64840,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1213" t="inlineStr"/>
       <c r="H1213" s="1" t="n">
         <v>0</v>
       </c>
@@ -65544,7 +64886,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1214" t="inlineStr"/>
       <c r="H1214" s="1" t="n">
         <v>0</v>
       </c>
@@ -65600,7 +64941,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1215" t="inlineStr"/>
       <c r="H1215" s="1" t="n">
         <v>0</v>
       </c>
@@ -65652,7 +64992,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1216" t="inlineStr"/>
       <c r="H1216" s="1" t="n">
         <v>0</v>
       </c>
@@ -65708,7 +65047,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1217" t="inlineStr"/>
       <c r="H1217" s="1" t="n">
         <v>0</v>
       </c>
@@ -65764,7 +65102,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1218" t="inlineStr"/>
       <c r="H1218" s="1" t="inlineStr"/>
       <c r="I1218" s="2" t="n"/>
       <c r="J1218" s="2" t="n"/>
@@ -65815,7 +65152,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1219" t="inlineStr"/>
       <c r="H1219" s="1" t="n">
         <v>0</v>
       </c>
@@ -65866,6 +65202,11 @@
           <t>Fixed</t>
         </is>
       </c>
+      <c r="I1220" s="2" t="inlineStr">
+        <is>
+          <t>676821061881</t>
+        </is>
+      </c>
       <c r="L1220" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -65906,7 +65247,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1221" t="inlineStr"/>
       <c r="H1221" s="1" t="inlineStr"/>
       <c r="I1221" s="2" t="n"/>
       <c r="J1221" s="2" t="n"/>
@@ -65959,7 +65299,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1222" t="inlineStr"/>
       <c r="H1222" s="1" t="n">
         <v>0</v>
       </c>
@@ -66015,7 +65354,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1223" t="inlineStr"/>
       <c r="H1223" s="1" t="inlineStr"/>
       <c r="I1223" s="2" t="inlineStr">
         <is>
@@ -66065,7 +65403,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1224" t="inlineStr"/>
       <c r="H1224" s="1" t="n">
         <v>0</v>
       </c>
@@ -66121,7 +65458,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1225" t="inlineStr"/>
       <c r="H1225" s="1" t="n">
         <v>0</v>
       </c>
@@ -66173,7 +65509,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1226" t="inlineStr"/>
       <c r="H1226" s="1" t="n">
         <v>0</v>
       </c>
@@ -66229,7 +65564,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1227" t="inlineStr"/>
       <c r="H1227" s="1" t="n">
         <v>0</v>
       </c>
@@ -66281,9 +65615,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1228" t="inlineStr"/>
       <c r="H1228" s="1" t="inlineStr"/>
-      <c r="I1228" s="2" t="n"/>
+      <c r="I1228" s="2" t="inlineStr">
+        <is>
+          <t>676821154972</t>
+        </is>
+      </c>
       <c r="J1228" s="2" t="n"/>
       <c r="K1228" s="2" t="inlineStr"/>
       <c r="L1228" s="2" t="inlineStr">
@@ -66337,7 +65674,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1229" t="inlineStr"/>
       <c r="H1229" s="1" t="n">
         <v>0</v>
       </c>
@@ -66513,7 +65849,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1232" t="inlineStr"/>
       <c r="H1232" s="1" t="inlineStr"/>
       <c r="I1232" s="2" t="inlineStr">
         <is>
@@ -66568,7 +65903,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1233" t="inlineStr"/>
       <c r="H1233" s="1" t="inlineStr"/>
       <c r="I1233" s="2" t="inlineStr">
         <is>
@@ -66628,7 +65962,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1234" t="inlineStr"/>
       <c r="H1234" s="1" t="n">
         <v>0</v>
       </c>
@@ -66675,7 +66008,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1235" t="inlineStr"/>
       <c r="H1235" s="1" t="n">
         <v>0</v>
       </c>
@@ -66731,7 +66063,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1236" t="inlineStr"/>
       <c r="H1236" s="1" t="inlineStr"/>
       <c r="I1236" s="2" t="inlineStr">
         <is>
@@ -66786,7 +66117,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1237" t="inlineStr"/>
       <c r="H1237" s="1" t="inlineStr"/>
       <c r="I1237" s="2" t="inlineStr">
         <is>
@@ -66841,7 +66171,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1238" t="inlineStr"/>
       <c r="H1238" s="1" t="n">
         <v>0</v>
       </c>
@@ -66897,7 +66226,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1239" t="inlineStr"/>
       <c r="H1239" s="1" t="n">
         <v>0</v>
       </c>
@@ -66963,7 +66291,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1241" t="inlineStr"/>
       <c r="H1241" s="1" t="n">
         <v>0</v>
       </c>
@@ -67014,7 +66341,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1242" t="inlineStr"/>
       <c r="H1242" s="1" t="n">
         <v>0</v>
       </c>
@@ -67061,7 +66387,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1243" t="inlineStr"/>
       <c r="H1243" s="1" t="inlineStr"/>
       <c r="I1243" s="2" t="n"/>
       <c r="J1243" s="2" t="n"/>
@@ -67117,7 +66442,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1244" t="inlineStr"/>
       <c r="H1244" s="1" t="inlineStr"/>
       <c r="I1244" s="2" t="inlineStr">
         <is>
@@ -67172,7 +66496,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1245" t="inlineStr"/>
       <c r="H1245" s="1" t="n">
         <v>0</v>
       </c>
@@ -67228,7 +66551,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1246" t="inlineStr"/>
       <c r="H1246" s="1" t="n">
         <v>0</v>
       </c>
@@ -67284,9 +66606,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1247" t="inlineStr"/>
       <c r="H1247" s="1" t="inlineStr"/>
-      <c r="I1247" s="2" t="n"/>
+      <c r="I1247" s="2" t="inlineStr">
+        <is>
+          <t>847294013060</t>
+        </is>
+      </c>
       <c r="J1247" s="2" t="n"/>
       <c r="K1247" s="2" t="inlineStr"/>
       <c r="L1247" s="2" t="inlineStr">
@@ -67335,7 +66660,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1248" t="inlineStr"/>
       <c r="H1248" s="1" t="inlineStr"/>
       <c r="I1248" s="2" t="inlineStr">
         <is>
@@ -67395,7 +66719,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1249" t="inlineStr"/>
       <c r="H1249" s="1" t="inlineStr"/>
       <c r="I1249" s="2" t="inlineStr">
         <is>
@@ -67515,7 +66838,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1251" t="inlineStr"/>
       <c r="H1251" s="1" t="n">
         <v>0</v>
       </c>
@@ -67568,7 +66890,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1252" t="inlineStr"/>
       <c r="H1252" s="1" t="n">
         <v>0</v>
       </c>
@@ -67625,7 +66946,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1253" t="inlineStr"/>
       <c r="H1253" s="1" t="inlineStr"/>
       <c r="I1253" s="2" t="n"/>
       <c r="J1253" s="2" t="n"/>
@@ -67686,7 +67006,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1255" t="inlineStr"/>
       <c r="H1255" s="1" t="n">
         <v>0</v>
       </c>
@@ -67733,7 +67052,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1256" t="inlineStr"/>
       <c r="H1256" s="1" t="inlineStr"/>
       <c r="I1256" s="2" t="inlineStr">
         <is>
@@ -67778,7 +67096,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1257" t="inlineStr"/>
       <c r="H1257" s="1" t="inlineStr"/>
       <c r="I1257" s="2" t="n"/>
       <c r="J1257" s="2" t="n"/>
@@ -67829,7 +67146,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1258" t="inlineStr"/>
       <c r="H1258" s="1" t="inlineStr"/>
       <c r="I1258" s="2" t="inlineStr">
         <is>
@@ -67884,7 +67200,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1259" t="inlineStr"/>
       <c r="H1259" s="1" t="inlineStr"/>
       <c r="I1259" s="2" t="inlineStr">
         <is>
@@ -67929,7 +67244,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1260" t="inlineStr"/>
       <c r="H1260" s="1" t="inlineStr"/>
       <c r="I1260" s="2" t="inlineStr">
         <is>
@@ -67984,7 +67298,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1261" t="inlineStr"/>
       <c r="H1261" s="1" t="n">
         <v>0</v>
       </c>
@@ -68040,7 +67353,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1262" t="inlineStr"/>
       <c r="H1262" s="1" t="n">
         <v>0</v>
       </c>
@@ -68099,7 +67411,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1264" t="inlineStr"/>
       <c r="H1264" s="1" t="inlineStr"/>
       <c r="I1264" s="2" t="inlineStr">
         <is>
@@ -68214,7 +67525,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1266" t="inlineStr"/>
       <c r="H1266" s="1" t="n">
         <v>0</v>
       </c>
@@ -68262,7 +67572,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1267" t="inlineStr"/>
       <c r="H1267" s="1" t="n">
         <v>0</v>
       </c>
@@ -68314,7 +67623,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1268" t="inlineStr"/>
       <c r="H1268" s="1" t="n">
         <v>0</v>
       </c>
@@ -68370,7 +67678,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1269" t="inlineStr"/>
       <c r="H1269" s="1" t="inlineStr"/>
       <c r="I1269" s="2" t="inlineStr">
         <is>
@@ -68427,7 +67734,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1270" t="inlineStr"/>
       <c r="H1270" s="1" t="n">
         <v>0</v>
       </c>
@@ -68474,7 +67780,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1271" t="inlineStr"/>
       <c r="H1271" s="1" t="inlineStr"/>
       <c r="I1271" s="2" t="inlineStr">
         <is>
@@ -68529,7 +67834,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1272" t="inlineStr"/>
       <c r="H1272" s="1" t="inlineStr"/>
       <c r="I1272" s="2" t="inlineStr">
         <is>
@@ -68579,7 +67883,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1273" t="inlineStr"/>
       <c r="H1273" s="1" t="n">
         <v>0</v>
       </c>
@@ -68635,7 +67938,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1274" t="inlineStr"/>
       <c r="H1274" s="1" t="inlineStr"/>
       <c r="I1274" s="2" t="inlineStr">
         <is>
@@ -68695,7 +67997,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1275" t="inlineStr"/>
       <c r="H1275" s="1" t="n">
         <v>0</v>
       </c>
@@ -68747,7 +68048,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1276" t="inlineStr"/>
       <c r="H1276" s="1" t="n">
         <v>0</v>
       </c>
@@ -68799,7 +68099,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1277" t="inlineStr"/>
       <c r="H1277" s="1" t="inlineStr"/>
       <c r="I1277" s="2" t="inlineStr">
         <is>
@@ -68859,7 +68158,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1278" t="inlineStr"/>
       <c r="H1278" s="1" t="n">
         <v>0</v>
       </c>
@@ -68915,7 +68213,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1279" t="inlineStr"/>
       <c r="H1279" s="1" t="n">
         <v>0</v>
       </c>
@@ -68973,7 +68270,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1280" t="inlineStr"/>
       <c r="H1280" s="1" t="n">
         <v>0</v>
       </c>
@@ -69020,7 +68316,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1281" t="inlineStr"/>
       <c r="H1281" s="1" t="n">
         <v>0</v>
       </c>
@@ -69067,7 +68362,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1282" t="inlineStr"/>
       <c r="H1282" s="1" t="n">
         <v>0</v>
       </c>
@@ -69119,7 +68413,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1283" t="inlineStr"/>
       <c r="H1283" s="1" t="inlineStr"/>
       <c r="I1283" s="2" t="inlineStr">
         <is>
@@ -69234,7 +68527,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1285" t="inlineStr"/>
       <c r="H1285" s="1" t="n">
         <v>0</v>
       </c>
@@ -69286,7 +68578,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1286" t="inlineStr"/>
       <c r="H1286" s="1" t="inlineStr"/>
       <c r="I1286" s="2" t="inlineStr">
         <is>
@@ -69341,7 +68632,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1287" t="inlineStr"/>
       <c r="H1287" s="1" t="n">
         <v>0</v>
       </c>
@@ -69388,7 +68678,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1288" t="inlineStr"/>
       <c r="H1288" s="1" t="inlineStr"/>
       <c r="I1288" s="2" t="inlineStr">
         <is>
@@ -69443,7 +68732,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1289" t="inlineStr"/>
       <c r="H1289" s="1" t="inlineStr"/>
       <c r="I1289" s="2" t="inlineStr">
         <is>
@@ -69553,7 +68841,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1291" t="inlineStr"/>
       <c r="H1291" s="1" t="n">
         <v>0</v>
       </c>
@@ -69609,7 +68896,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1292" t="inlineStr"/>
       <c r="H1292" s="1" t="n">
         <v>0</v>
       </c>
@@ -69656,7 +68942,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1293" t="inlineStr"/>
       <c r="H1293" s="1" t="inlineStr"/>
       <c r="I1293" s="2" t="inlineStr">
         <is>
@@ -69711,7 +68996,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1294" t="inlineStr"/>
       <c r="H1294" s="1" t="inlineStr"/>
       <c r="I1294" s="2" t="n"/>
       <c r="J1294" s="2" t="n"/>
@@ -69827,7 +69111,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1296" t="inlineStr"/>
       <c r="H1296" s="1" t="n">
         <v>0</v>
       </c>
@@ -69883,7 +69166,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1297" t="inlineStr"/>
       <c r="H1297" s="1" t="n">
         <v>0</v>
       </c>
@@ -69995,7 +69277,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1299" t="inlineStr"/>
       <c r="H1299" s="1" t="n">
         <v>0</v>
       </c>
@@ -70122,7 +69403,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1302" t="inlineStr"/>
       <c r="H1302" s="1" t="n">
         <v>6.99</v>
       </c>
@@ -70184,9 +69464,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1303" t="inlineStr"/>
       <c r="H1303" s="1" t="inlineStr"/>
-      <c r="I1303" s="2" t="n"/>
+      <c r="I1303" s="2" t="inlineStr">
+        <is>
+          <t>676821336750</t>
+        </is>
+      </c>
       <c r="J1303" s="2" t="n"/>
       <c r="K1303" s="2" t="inlineStr"/>
       <c r="L1303" s="2" t="inlineStr">
@@ -70235,7 +69518,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1304" t="inlineStr"/>
       <c r="H1304" s="1" t="inlineStr"/>
       <c r="I1304" s="2" t="inlineStr">
         <is>
@@ -70290,7 +69572,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1305" t="inlineStr"/>
       <c r="H1305" s="1" t="inlineStr"/>
       <c r="I1305" s="2" t="inlineStr">
         <is>
@@ -70345,7 +69626,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1306" t="inlineStr"/>
       <c r="H1306" s="1" t="inlineStr"/>
       <c r="I1306" s="2" t="inlineStr">
         <is>
@@ -70400,7 +69680,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1307" t="inlineStr"/>
       <c r="H1307" s="1" t="n">
         <v>0</v>
       </c>
@@ -70457,7 +69736,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1308" t="inlineStr"/>
       <c r="H1308" s="1" t="n">
         <v>0</v>
       </c>
@@ -70504,7 +69782,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1309" t="inlineStr"/>
       <c r="H1309" s="1" t="inlineStr"/>
       <c r="I1309" s="2" t="n"/>
       <c r="J1309" s="2" t="n"/>
@@ -70560,7 +69837,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1310" t="inlineStr"/>
       <c r="H1310" s="1" t="n">
         <v>0</v>
       </c>
@@ -70676,7 +69952,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1312" t="inlineStr"/>
       <c r="H1312" s="1" t="n">
         <v>0</v>
       </c>
@@ -70738,7 +70013,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1313" t="inlineStr"/>
       <c r="H1313" s="1" t="inlineStr"/>
       <c r="I1313" s="2" t="inlineStr">
         <is>
@@ -70788,7 +70062,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1314" t="inlineStr"/>
       <c r="H1314" s="1" t="n">
         <v>0</v>
       </c>
@@ -70850,9 +70123,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1315" t="inlineStr"/>
       <c r="H1315" s="1" t="inlineStr"/>
-      <c r="I1315" s="2" t="n"/>
+      <c r="I1315" s="2" t="inlineStr">
+        <is>
+          <t>847294002729</t>
+        </is>
+      </c>
       <c r="J1315" s="2" t="n"/>
       <c r="K1315" s="2" t="inlineStr"/>
       <c r="L1315" s="2" t="inlineStr">
@@ -70957,7 +70233,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1317" t="inlineStr"/>
       <c r="H1317" s="1" t="n">
         <v>0</v>
       </c>
@@ -71014,7 +70289,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1318" t="inlineStr"/>
       <c r="H1318" s="1" t="inlineStr"/>
       <c r="I1318" s="2" t="inlineStr">
         <is>
@@ -71079,7 +70353,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1320" t="inlineStr"/>
       <c r="H1320" s="1" t="inlineStr"/>
       <c r="I1320" s="2" t="n"/>
       <c r="J1320" s="2" t="n"/>
@@ -71190,7 +70463,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1322" t="inlineStr"/>
       <c r="H1322" s="1" t="inlineStr"/>
       <c r="I1322" s="2" t="inlineStr">
         <is>
@@ -71245,7 +70517,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1323" t="inlineStr"/>
       <c r="H1323" s="1" t="n">
         <v>0</v>
       </c>
@@ -71301,7 +70572,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1324" t="inlineStr"/>
       <c r="H1324" s="1" t="n">
         <v>0</v>
       </c>
@@ -71358,9 +70628,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1325" t="inlineStr"/>
       <c r="H1325" s="1" t="inlineStr"/>
-      <c r="I1325" s="2" t="n"/>
+      <c r="I1325" s="2" t="inlineStr">
+        <is>
+          <t>847294095929</t>
+        </is>
+      </c>
       <c r="J1325" s="2" t="n"/>
       <c r="K1325" s="2" t="inlineStr"/>
       <c r="L1325" s="2" t="inlineStr">
@@ -71409,7 +70682,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1326" t="inlineStr"/>
       <c r="H1326" s="1" t="n">
         <v>0</v>
       </c>
@@ -71465,7 +70737,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1327" t="inlineStr"/>
       <c r="H1327" s="1" t="inlineStr"/>
       <c r="I1327" s="2" t="inlineStr">
         <is>
@@ -71522,7 +70793,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1328" t="inlineStr"/>
       <c r="H1328" s="1" t="inlineStr"/>
       <c r="I1328" s="2" t="inlineStr">
         <is>
@@ -71577,7 +70847,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1329" t="inlineStr"/>
       <c r="H1329" s="1" t="inlineStr"/>
       <c r="I1329" s="2" t="inlineStr">
         <is>
@@ -71627,7 +70896,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1330" t="inlineStr"/>
       <c r="H1330" s="1" t="n">
         <v>0</v>
       </c>
@@ -71739,7 +71007,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1332" t="inlineStr"/>
       <c r="H1332" s="1" t="n">
         <v>0</v>
       </c>
@@ -71786,7 +71053,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1333" t="inlineStr"/>
       <c r="H1333" s="1" t="n">
         <v>0</v>
       </c>
@@ -71902,7 +71168,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1335" t="inlineStr"/>
       <c r="H1335" s="1" t="n">
         <v>0</v>
       </c>
@@ -71958,7 +71223,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1336" t="inlineStr"/>
       <c r="H1336" s="1" t="n">
         <v>0</v>
       </c>
@@ -72019,7 +71283,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1337" t="inlineStr"/>
       <c r="H1337" s="1" t="n">
         <v>0</v>
       </c>
@@ -72075,7 +71338,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1338" t="inlineStr"/>
       <c r="H1338" s="1" t="n">
         <v>0</v>
       </c>
@@ -72127,7 +71389,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1339" t="inlineStr"/>
       <c r="H1339" s="1" t="inlineStr"/>
       <c r="I1339" s="2" t="inlineStr">
         <is>
@@ -72237,7 +71498,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="G1341" t="inlineStr"/>
       <c r="H1341" s="1" t="n">
         <v>0</v>
       </c>

--- a/inventoryexportv2_1_updated.xlsx
+++ b/inventoryexportv2_1_updated.xlsx
@@ -249,7 +249,7 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="40" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -372,6 +372,9 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3010,7 +3013,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>813559002452</t>
+          <t>847294034553</t>
         </is>
       </c>
       <c r="J30" s="2" t="n"/>
@@ -3120,7 +3123,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>000000110426</t>
+          <t>8472940071201</t>
         </is>
       </c>
       <c r="J32" s="2" t="n"/>
@@ -3169,7 +3172,7 @@
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>847294007120</t>
+          <t>8472940071201</t>
         </is>
       </c>
       <c r="J33" s="2" t="n"/>
@@ -3572,7 +3575,11 @@
         </is>
       </c>
       <c r="H41" s="1" t="inlineStr"/>
-      <c r="I41" s="2" t="n"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>676821102836</t>
+        </is>
+      </c>
       <c r="J41" s="2" t="n"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
@@ -4687,7 +4694,11 @@
         </is>
       </c>
       <c r="H62" s="1" t="inlineStr"/>
-      <c r="I62" s="2" t="n"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>847294014050</t>
+        </is>
+      </c>
       <c r="J62" s="2" t="n"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
@@ -5890,7 +5901,11 @@
         </is>
       </c>
       <c r="H85" s="1" t="inlineStr"/>
-      <c r="I85" s="2" t="n"/>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>847294004709</t>
+        </is>
+      </c>
       <c r="J85" s="2" t="n"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
@@ -6007,11 +6022,7 @@
       <c r="H87" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>847294039251</t>
-        </is>
-      </c>
+      <c r="I87" s="2" t="n"/>
       <c r="J87" s="2" t="n"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
@@ -6363,7 +6374,11 @@
         </is>
       </c>
       <c r="H94" s="1" t="inlineStr"/>
-      <c r="I94" s="2" t="n"/>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>847294039251</t>
+        </is>
+      </c>
       <c r="J94" s="2" t="n"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
@@ -6726,7 +6741,7 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>47294095325</t>
+          <t>847294095325</t>
         </is>
       </c>
       <c r="J101" s="2" t="n"/>
@@ -7444,7 +7459,7 @@
       <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>6950165406657</t>
+          <t>847294016825</t>
         </is>
       </c>
       <c r="J114" s="2" t="n"/>
@@ -8156,7 +8171,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>729205027895</t>
+          <t>847294045207</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -8722,7 +8737,7 @@
       <c r="H139" s="1" t="inlineStr"/>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>847294016825</t>
+          <t>847294094571</t>
         </is>
       </c>
       <c r="J139" s="2" t="n"/>
@@ -9047,7 +9062,7 @@
       <c r="H145" s="1" t="inlineStr"/>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>601527870376</t>
+          <t>601527824386</t>
         </is>
       </c>
       <c r="J145" s="2" t="n"/>
@@ -11720,7 +11735,7 @@
       <c r="H193" s="1" t="inlineStr"/>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>676821258557</t>
+          <t>847294008622</t>
         </is>
       </c>
       <c r="J193" s="2" t="n"/>
@@ -12541,7 +12556,7 @@
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>47294090498</t>
+          <t>847294004648</t>
         </is>
       </c>
       <c r="J208" s="2" t="inlineStr">
@@ -13681,7 +13696,7 @@
       <c r="H229" s="1" t="inlineStr"/>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>847294089058</t>
+          <t>847294020167</t>
         </is>
       </c>
       <c r="J229" s="2" t="n"/>
@@ -13852,7 +13867,7 @@
       <c r="H232" s="1" t="inlineStr"/>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>847294041124</t>
+          <t>847294029184</t>
         </is>
       </c>
       <c r="J232" s="2" t="n"/>
@@ -14237,7 +14252,11 @@
         </is>
       </c>
       <c r="H239" s="1" t="inlineStr"/>
-      <c r="I239" s="2" t="n"/>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>847294094991</t>
+        </is>
+      </c>
       <c r="J239" s="2" t="n"/>
       <c r="K239" s="2" t="inlineStr"/>
       <c r="L239" s="2" t="inlineStr">
@@ -15003,7 +15022,11 @@
         </is>
       </c>
       <c r="H253" s="1" t="inlineStr"/>
-      <c r="I253" s="2" t="n"/>
+      <c r="I253" s="2" t="inlineStr">
+        <is>
+          <t>676821258557</t>
+        </is>
+      </c>
       <c r="J253" s="2" t="n"/>
       <c r="K253" s="2" t="inlineStr"/>
       <c r="L253" s="2" t="inlineStr">
@@ -15726,7 +15749,7 @@
       <c r="H266" s="1" t="inlineStr"/>
       <c r="I266" s="2" t="inlineStr">
         <is>
-          <t>847294004709</t>
+          <t>676821085986</t>
         </is>
       </c>
       <c r="J266" s="2" t="n"/>
@@ -17667,11 +17690,7 @@
         </is>
       </c>
       <c r="H303" s="1" t="inlineStr"/>
-      <c r="I303" s="2" t="inlineStr">
-        <is>
-          <t>676821310378</t>
-        </is>
-      </c>
+      <c r="I303" s="2" t="n"/>
       <c r="J303" s="2" t="n"/>
       <c r="K303" s="2" t="inlineStr"/>
       <c r="L303" s="2" t="inlineStr">
@@ -20246,7 +20265,7 @@
       <c r="H352" s="1" t="inlineStr"/>
       <c r="I352" s="2" t="inlineStr">
         <is>
-          <t>676821085986</t>
+          <t>847294009049</t>
         </is>
       </c>
       <c r="J352" s="2" t="n"/>
@@ -20356,7 +20375,7 @@
       <c r="H354" s="1" t="inlineStr"/>
       <c r="I354" s="2" t="inlineStr">
         <is>
-          <t>676821077042</t>
+          <t>847294085586</t>
         </is>
       </c>
       <c r="J354" s="2" t="n"/>
@@ -20475,7 +20494,7 @@
       <c r="H356" s="1" t="inlineStr"/>
       <c r="I356" s="2" t="inlineStr">
         <is>
-          <t>847294042039</t>
+          <t>847294085593</t>
         </is>
       </c>
       <c r="J356" s="2" t="n"/>
@@ -20594,7 +20613,7 @@
       <c r="H358" s="1" t="inlineStr"/>
       <c r="I358" s="2" t="inlineStr">
         <is>
-          <t>676821433930</t>
+          <t>847294085647</t>
         </is>
       </c>
       <c r="J358" s="2" t="n"/>
@@ -23022,7 +23041,7 @@
       </c>
       <c r="I402" s="2" t="inlineStr">
         <is>
-          <t>950165402499</t>
+          <t>6950165407499</t>
         </is>
       </c>
       <c r="J402" s="2" t="n"/>
@@ -23138,7 +23157,7 @@
       </c>
       <c r="I404" s="2" t="inlineStr">
         <is>
-          <t>950165402482</t>
+          <t>6950165407499</t>
         </is>
       </c>
       <c r="J404" s="2" t="n"/>
@@ -23567,7 +23586,7 @@
       <c r="H412" s="1" t="inlineStr"/>
       <c r="I412" s="2" t="inlineStr">
         <is>
-          <t>6950165415840</t>
+          <t>847294031453</t>
         </is>
       </c>
       <c r="J412" s="2" t="n"/>
@@ -23678,7 +23697,7 @@
       </c>
       <c r="I414" s="2" t="inlineStr">
         <is>
-          <t>875330061706</t>
+          <t>676821143167</t>
         </is>
       </c>
       <c r="J414" s="2" t="inlineStr">
@@ -24412,7 +24431,7 @@
       <c r="H428" s="1" t="inlineStr"/>
       <c r="I428" s="2" t="inlineStr">
         <is>
-          <t>676821266873</t>
+          <t>847294042039</t>
         </is>
       </c>
       <c r="J428" s="2" t="n"/>
@@ -24714,7 +24733,7 @@
       </c>
       <c r="I434" s="2" t="inlineStr">
         <is>
-          <t>847294031019</t>
+          <t>847294031002</t>
         </is>
       </c>
       <c r="J434" s="2" t="n"/>
@@ -24768,7 +24787,7 @@
       <c r="H435" s="1" t="inlineStr"/>
       <c r="I435" s="2" t="inlineStr">
         <is>
-          <t>847294031019</t>
+          <t>847294031002</t>
         </is>
       </c>
       <c r="J435" s="2" t="n"/>
@@ -26287,7 +26306,7 @@
       </c>
       <c r="I463" s="2" t="inlineStr">
         <is>
-          <t>8145270502815</t>
+          <t>847294036984</t>
         </is>
       </c>
       <c r="J463" s="2" t="inlineStr">
@@ -29481,7 +29500,7 @@
       </c>
       <c r="I522" s="2" t="inlineStr">
         <is>
-          <t>875330063908</t>
+          <t>676821135438</t>
         </is>
       </c>
       <c r="J522" s="2" t="inlineStr">
@@ -30014,7 +30033,11 @@
         </is>
       </c>
       <c r="H532" s="1" t="inlineStr"/>
-      <c r="I532" s="2" t="n"/>
+      <c r="I532" s="2" t="inlineStr">
+        <is>
+          <t>676821439659</t>
+        </is>
+      </c>
       <c r="J532" s="2" t="n"/>
       <c r="K532" s="2" t="inlineStr"/>
       <c r="L532" s="2" t="inlineStr">
@@ -30129,7 +30152,11 @@
         </is>
       </c>
       <c r="H534" s="1" t="inlineStr"/>
-      <c r="I534" s="2" t="n"/>
+      <c r="I534" s="2" t="inlineStr">
+        <is>
+          <t>676821433930</t>
+        </is>
+      </c>
       <c r="J534" s="2" t="n"/>
       <c r="K534" s="2" t="inlineStr"/>
       <c r="L534" s="2" t="inlineStr">
@@ -32076,7 +32103,11 @@
         </is>
       </c>
       <c r="H571" s="1" t="inlineStr"/>
-      <c r="I571" s="2" t="n"/>
+      <c r="I571" s="2" t="inlineStr">
+        <is>
+          <t>847294009254</t>
+        </is>
+      </c>
       <c r="J571" s="2" t="n"/>
       <c r="K571" s="2" t="inlineStr"/>
       <c r="L571" s="2" t="inlineStr">
@@ -33188,7 +33219,7 @@
       </c>
       <c r="I592" s="2" t="inlineStr">
         <is>
-          <t>47294092485</t>
+          <t>847294092485</t>
         </is>
       </c>
       <c r="J592" s="2" t="n"/>
@@ -33394,7 +33425,7 @@
       <c r="H596" s="1" t="inlineStr"/>
       <c r="I596" s="2" t="inlineStr">
         <is>
-          <t>193836410928</t>
+          <t>676821059819</t>
         </is>
       </c>
       <c r="J596" s="2" t="n"/>
@@ -33672,7 +33703,7 @@
       </c>
       <c r="I601" s="2" t="inlineStr">
         <is>
-          <t>676821122988</t>
+          <t>676821310378</t>
         </is>
       </c>
       <c r="J601" s="2" t="n"/>
@@ -36521,7 +36552,7 @@
       </c>
       <c r="I657" s="2" t="inlineStr">
         <is>
-          <t>193836404620</t>
+          <t>847294041926</t>
         </is>
       </c>
       <c r="J657" s="2" t="n"/>
@@ -36577,7 +36608,7 @@
       <c r="H658" s="1" t="inlineStr"/>
       <c r="I658" s="2" t="inlineStr">
         <is>
-          <t>47294041926</t>
+          <t>847294041926</t>
         </is>
       </c>
       <c r="J658" s="2" t="n"/>
@@ -36628,7 +36659,7 @@
       <c r="H659" s="1" t="inlineStr"/>
       <c r="I659" s="2" t="inlineStr">
         <is>
-          <t>676821102836</t>
+          <t>847294041926</t>
         </is>
       </c>
       <c r="J659" s="2" t="n"/>
@@ -41003,11 +41034,7 @@
         </is>
       </c>
       <c r="H743" s="1" t="inlineStr"/>
-      <c r="I743" s="2" t="inlineStr">
-        <is>
-          <t>676821439659</t>
-        </is>
-      </c>
+      <c r="I743" s="2" t="n"/>
       <c r="J743" s="2" t="n"/>
       <c r="K743" s="2" t="inlineStr"/>
       <c r="L743" s="2" t="inlineStr">
@@ -43040,11 +43067,7 @@
         </is>
       </c>
       <c r="H782" s="1" t="inlineStr"/>
-      <c r="I782" s="2" t="inlineStr">
-        <is>
-          <t>847294001463</t>
-        </is>
-      </c>
+      <c r="I782" s="2" t="n"/>
       <c r="J782" s="2" t="n"/>
       <c r="K782" s="2" t="inlineStr"/>
       <c r="L782" s="2" t="inlineStr">
@@ -43899,7 +43922,7 @@
       </c>
       <c r="I801" s="2" t="inlineStr">
         <is>
-          <t>6950165409283</t>
+          <t>847294025391</t>
         </is>
       </c>
       <c r="J801" s="2" t="inlineStr">
@@ -45142,7 +45165,7 @@
       </c>
       <c r="I826" s="2" t="inlineStr">
         <is>
-          <t>847294016849</t>
+          <t>847294096469</t>
         </is>
       </c>
       <c r="J826" s="2" t="inlineStr">
@@ -45307,7 +45330,11 @@
         </is>
       </c>
       <c r="H829" s="1" t="inlineStr"/>
-      <c r="I829" s="2" t="n"/>
+      <c r="I829" s="2" t="inlineStr">
+        <is>
+          <t>6950165415840</t>
+        </is>
+      </c>
       <c r="J829" s="2" t="n"/>
       <c r="K829" s="2" t="inlineStr"/>
       <c r="L829" s="2" t="inlineStr">
@@ -45677,7 +45704,7 @@
       </c>
       <c r="I836" s="2" t="inlineStr">
         <is>
-          <t>652009003409</t>
+          <t>847294019116</t>
         </is>
       </c>
       <c r="J836" s="2" t="inlineStr">
@@ -46275,7 +46302,7 @@
       </c>
       <c r="I847" s="2" t="inlineStr">
         <is>
-          <t>145270102121</t>
+          <t>676821186195</t>
         </is>
       </c>
       <c r="J847" s="2" t="n"/>
@@ -49563,7 +49590,7 @@
       </c>
       <c r="I915" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>676821266873</t>
         </is>
       </c>
       <c r="J915" s="2" t="n"/>
@@ -49662,7 +49689,7 @@
       <c r="H917" s="1" t="inlineStr"/>
       <c r="I917" s="2" t="inlineStr">
         <is>
-          <t>847294014050</t>
+          <t>676821266873</t>
         </is>
       </c>
       <c r="J917" s="2" t="n"/>
@@ -50393,7 +50420,7 @@
       <c r="H930" s="1" t="inlineStr"/>
       <c r="I930" s="2" t="inlineStr">
         <is>
-          <t>753459922682</t>
+          <t>676821106629</t>
         </is>
       </c>
       <c r="J930" s="2" t="n"/>
@@ -53101,7 +53128,7 @@
       <c r="H985" s="1" t="inlineStr"/>
       <c r="I985" s="2" t="inlineStr">
         <is>
-          <t>813559007501</t>
+          <t>847294030920</t>
         </is>
       </c>
       <c r="J985" s="2" t="n"/>
@@ -54136,7 +54163,11 @@
         </is>
       </c>
       <c r="H1005" s="1" t="inlineStr"/>
-      <c r="I1005" s="2" t="n"/>
+      <c r="I1005" s="2" t="inlineStr">
+        <is>
+          <t>847294085982</t>
+        </is>
+      </c>
       <c r="J1005" s="2" t="n"/>
       <c r="K1005" s="2" t="inlineStr"/>
       <c r="L1005" s="2" t="inlineStr">
@@ -55265,7 +55296,7 @@
       <c r="H1027" s="1" t="inlineStr"/>
       <c r="I1027" s="2" t="inlineStr">
         <is>
-          <t>875330020208</t>
+          <t>847294092423</t>
         </is>
       </c>
       <c r="J1027" s="2" t="n"/>
@@ -55316,7 +55347,7 @@
       </c>
       <c r="I1028" s="2" t="inlineStr">
         <is>
-          <t>75330020208</t>
+          <t>847294092423</t>
         </is>
       </c>
       <c r="J1028" s="2" t="n"/>
@@ -56450,7 +56481,7 @@
       </c>
       <c r="I1049" s="2" t="inlineStr">
         <is>
-          <t>695016540307</t>
+          <t>6950165403014</t>
         </is>
       </c>
       <c r="J1049" s="2" t="inlineStr">
@@ -57768,8 +57799,10 @@
       <c r="H1075" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I1075" s="44" t="n">
-        <v>847294098395</v>
+      <c r="I1075" s="48" t="inlineStr">
+        <is>
+          <t>676821466891</t>
+        </is>
       </c>
       <c r="J1075" s="44" t="n">
         <v>847294098395</v>
@@ -57919,7 +57952,7 @@
       <c r="H1078" s="1" t="inlineStr"/>
       <c r="I1078" s="2" t="inlineStr">
         <is>
-          <t>847294012124</t>
+          <t>676821478092</t>
         </is>
       </c>
       <c r="J1078" s="2" t="n"/>
@@ -58713,11 +58746,7 @@
       <c r="H1096" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I1096" s="2" t="inlineStr">
-        <is>
-          <t>847294042022</t>
-        </is>
-      </c>
+      <c r="I1096" s="2" t="n"/>
       <c r="J1096" s="2" t="inlineStr">
         <is>
           <t>847294042022</t>
@@ -62334,7 +62363,7 @@
       <c r="H1165" s="1" t="inlineStr"/>
       <c r="I1165" s="2" t="inlineStr">
         <is>
-          <t>47294013145</t>
+          <t>847294013145</t>
         </is>
       </c>
       <c r="J1165" s="2" t="n"/>
@@ -63166,7 +63195,7 @@
       <c r="H1181" s="1" t="inlineStr"/>
       <c r="I1181" s="2" t="inlineStr">
         <is>
-          <t>6950165409382</t>
+          <t>847294008042</t>
         </is>
       </c>
       <c r="J1181" s="2" t="n"/>
@@ -63630,7 +63659,7 @@
       </c>
       <c r="I1190" s="2" t="inlineStr">
         <is>
-          <t>6944112605170</t>
+          <t>805253516328</t>
         </is>
       </c>
       <c r="J1190" s="2" t="inlineStr">
@@ -63683,7 +63712,7 @@
       <c r="H1191" s="1" t="inlineStr"/>
       <c r="I1191" s="2" t="inlineStr">
         <is>
-          <t>847294029184</t>
+          <t>847294004129</t>
         </is>
       </c>
       <c r="J1191" s="2" t="n"/>
@@ -64467,7 +64496,7 @@
       <c r="H1206" s="1" t="inlineStr"/>
       <c r="I1206" s="2" t="inlineStr">
         <is>
-          <t>47294040332</t>
+          <t>6950165408477</t>
         </is>
       </c>
       <c r="J1206" s="2" t="n"/>
@@ -65463,7 +65492,7 @@
       </c>
       <c r="I1225" s="2" t="inlineStr">
         <is>
-          <t>950165407098</t>
+          <t>6944112600366</t>
         </is>
       </c>
       <c r="J1225" s="2" t="n"/>
@@ -66663,7 +66692,7 @@
       <c r="H1248" s="1" t="inlineStr"/>
       <c r="I1248" s="2" t="inlineStr">
         <is>
-          <t>847294039022</t>
+          <t>676821374431</t>
         </is>
       </c>
       <c r="J1248" s="2" t="n"/>
@@ -67783,7 +67812,7 @@
       <c r="H1271" s="1" t="inlineStr"/>
       <c r="I1271" s="2" t="inlineStr">
         <is>
-          <t>847294006178</t>
+          <t>847294008417</t>
         </is>
       </c>
       <c r="J1271" s="2" t="n"/>
@@ -68102,7 +68131,7 @@
       <c r="H1277" s="1" t="inlineStr"/>
       <c r="I1277" s="2" t="inlineStr">
         <is>
-          <t>847294094991</t>
+          <t>847294096315</t>
         </is>
       </c>
       <c r="J1277" s="2" t="n"/>
@@ -71559,7 +71588,7 @@
       </c>
       <c r="I1342" s="2" t="inlineStr">
         <is>
-          <t>847294017075</t>
+          <t>847294092515</t>
         </is>
       </c>
       <c r="J1342" s="2" t="inlineStr">
@@ -71667,8 +71696,10 @@
           <t>Home Run</t>
         </is>
       </c>
-      <c r="I1346" s="45" t="n">
-        <v>193836410928</v>
+      <c r="I1346" s="2" t="inlineStr">
+        <is>
+          <t>676821059819</t>
+        </is>
       </c>
     </row>
     <row r="1347">
@@ -71720,9 +71751,7 @@
           <t>Captain Marvel</t>
         </is>
       </c>
-      <c r="I1352" s="45" t="n">
-        <v>847294030272</v>
-      </c>
+      <c r="I1352" s="45" t="n"/>
     </row>
     <row r="1353">
       <c r="B1353" t="inlineStr">
@@ -71840,8 +71869,10 @@
           <t>blast zone</t>
         </is>
       </c>
-      <c r="I1364" s="45" t="n">
-        <v>753459937747</v>
+      <c r="I1364" s="2" t="inlineStr">
+        <is>
+          <t>676821076113</t>
+        </is>
       </c>
     </row>
     <row r="1365">

--- a/inventoryexportv2_1_updated.xlsx
+++ b/inventoryexportv2_1_updated.xlsx
@@ -65132,7 +65132,11 @@
         </is>
       </c>
       <c r="H1218" s="1" t="inlineStr"/>
-      <c r="I1218" s="2" t="n"/>
+      <c r="I1218" s="2" t="inlineStr">
+        <is>
+          <t>757205301226</t>
+        </is>
+      </c>
       <c r="J1218" s="2" t="n"/>
       <c r="K1218" s="2" t="inlineStr"/>
       <c r="L1218" s="2" t="inlineStr">
